--- a/output/version3/test/15-5/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>602</v>
+        <v>668</v>
       </c>
       <c r="C2" t="n">
-        <v>649</v>
+        <v>636</v>
       </c>
       <c r="D2" t="n">
-        <v>594</v>
+        <v>632</v>
       </c>
       <c r="E2" t="n">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="F2" t="n">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="G2" t="n">
-        <v>618</v>
+        <v>646</v>
       </c>
       <c r="H2" t="n">
-        <v>642</v>
+        <v>678</v>
       </c>
       <c r="I2" t="n">
-        <v>543</v>
+        <v>590</v>
       </c>
       <c r="J2" t="n">
-        <v>598</v>
+        <v>638</v>
       </c>
       <c r="K2" t="n">
-        <v>602</v>
+        <v>691</v>
       </c>
       <c r="L2" t="n">
-        <v>619.4</v>
+        <v>650.8</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>682</v>
+        <v>731</v>
       </c>
       <c r="C3" t="n">
-        <v>645</v>
+        <v>756</v>
       </c>
       <c r="D3" t="n">
-        <v>711</v>
+        <v>733</v>
       </c>
       <c r="E3" t="n">
-        <v>737</v>
+        <v>691</v>
       </c>
       <c r="F3" t="n">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="G3" t="n">
-        <v>636</v>
+        <v>714</v>
       </c>
       <c r="H3" t="n">
-        <v>807</v>
+        <v>890</v>
       </c>
       <c r="I3" t="n">
-        <v>752</v>
+        <v>689</v>
       </c>
       <c r="J3" t="n">
-        <v>762</v>
+        <v>798</v>
       </c>
       <c r="K3" t="n">
-        <v>772</v>
+        <v>756</v>
       </c>
       <c r="L3" t="n">
-        <v>726.8</v>
+        <v>751.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>645</v>
+        <v>670</v>
       </c>
       <c r="C4" t="n">
-        <v>728</v>
+        <v>762</v>
       </c>
       <c r="D4" t="n">
-        <v>672</v>
+        <v>762</v>
       </c>
       <c r="E4" t="n">
-        <v>778</v>
+        <v>835</v>
       </c>
       <c r="F4" t="n">
-        <v>653</v>
+        <v>743</v>
       </c>
       <c r="G4" t="n">
-        <v>728</v>
+        <v>668</v>
       </c>
       <c r="H4" t="n">
-        <v>678</v>
+        <v>712</v>
       </c>
       <c r="I4" t="n">
-        <v>696</v>
+        <v>742</v>
       </c>
       <c r="J4" t="n">
-        <v>735</v>
+        <v>707</v>
       </c>
       <c r="K4" t="n">
-        <v>823</v>
+        <v>857</v>
       </c>
       <c r="L4" t="n">
-        <v>713.6</v>
+        <v>745.8</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>771</v>
+        <v>809</v>
       </c>
       <c r="C5" t="n">
+        <v>908</v>
+      </c>
+      <c r="D5" t="n">
+        <v>818</v>
+      </c>
+      <c r="E5" t="n">
+        <v>885</v>
+      </c>
+      <c r="F5" t="n">
+        <v>852</v>
+      </c>
+      <c r="G5" t="n">
+        <v>808</v>
+      </c>
+      <c r="H5" t="n">
+        <v>786</v>
+      </c>
+      <c r="I5" t="n">
         <v>814</v>
       </c>
-      <c r="D5" t="n">
-        <v>866</v>
-      </c>
-      <c r="E5" t="n">
-        <v>834</v>
-      </c>
-      <c r="F5" t="n">
-        <v>876</v>
-      </c>
-      <c r="G5" t="n">
-        <v>872</v>
-      </c>
-      <c r="H5" t="n">
-        <v>779</v>
-      </c>
-      <c r="I5" t="n">
-        <v>865</v>
-      </c>
       <c r="J5" t="n">
-        <v>821</v>
+        <v>892</v>
       </c>
       <c r="K5" t="n">
-        <v>837</v>
+        <v>904</v>
       </c>
       <c r="L5" t="n">
-        <v>833.5</v>
+        <v>847.6</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>657</v>
+        <v>649</v>
       </c>
       <c r="C6" t="n">
+        <v>612</v>
+      </c>
+      <c r="D6" t="n">
         <v>644</v>
       </c>
-      <c r="D6" t="n">
-        <v>690</v>
-      </c>
       <c r="E6" t="n">
-        <v>685</v>
+        <v>653</v>
       </c>
       <c r="F6" t="n">
-        <v>677</v>
+        <v>619</v>
       </c>
       <c r="G6" t="n">
-        <v>711</v>
+        <v>720</v>
       </c>
       <c r="H6" t="n">
-        <v>581</v>
+        <v>684</v>
       </c>
       <c r="I6" t="n">
-        <v>600</v>
+        <v>637</v>
       </c>
       <c r="J6" t="n">
-        <v>657</v>
+        <v>717</v>
       </c>
       <c r="K6" t="n">
-        <v>681</v>
+        <v>666</v>
       </c>
       <c r="L6" t="n">
-        <v>658.3</v>
+        <v>660.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>707</v>
+        <v>759</v>
       </c>
       <c r="C7" t="n">
-        <v>708</v>
+        <v>832</v>
       </c>
       <c r="D7" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="E7" t="n">
-        <v>717</v>
+        <v>876</v>
       </c>
       <c r="F7" t="n">
-        <v>774</v>
+        <v>763</v>
       </c>
       <c r="G7" t="n">
-        <v>777</v>
+        <v>747</v>
       </c>
       <c r="H7" t="n">
-        <v>744</v>
+        <v>977</v>
       </c>
       <c r="I7" t="n">
-        <v>786</v>
+        <v>764</v>
       </c>
       <c r="J7" t="n">
-        <v>746</v>
+        <v>785</v>
       </c>
       <c r="K7" t="n">
-        <v>755</v>
+        <v>825</v>
       </c>
       <c r="L7" t="n">
-        <v>741.5</v>
+        <v>802.1</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>588</v>
+        <v>673</v>
       </c>
       <c r="C8" t="n">
-        <v>655</v>
+        <v>733</v>
       </c>
       <c r="D8" t="n">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="E8" t="n">
-        <v>782</v>
+        <v>636</v>
       </c>
       <c r="F8" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="G8" t="n">
-        <v>677</v>
+        <v>616</v>
       </c>
       <c r="H8" t="n">
-        <v>657</v>
+        <v>667</v>
       </c>
       <c r="I8" t="n">
-        <v>688</v>
+        <v>775</v>
       </c>
       <c r="J8" t="n">
-        <v>612</v>
+        <v>756</v>
       </c>
       <c r="K8" t="n">
-        <v>642</v>
+        <v>684</v>
       </c>
       <c r="L8" t="n">
-        <v>663.3</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>771</v>
+        <v>636</v>
       </c>
       <c r="C9" t="n">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="D9" t="n">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="E9" t="n">
-        <v>587</v>
+        <v>784</v>
       </c>
       <c r="F9" t="n">
-        <v>589</v>
+        <v>657</v>
       </c>
       <c r="G9" t="n">
-        <v>619</v>
+        <v>647</v>
       </c>
       <c r="H9" t="n">
-        <v>733</v>
+        <v>659</v>
       </c>
       <c r="I9" t="n">
-        <v>637</v>
+        <v>698</v>
       </c>
       <c r="J9" t="n">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="K9" t="n">
-        <v>647</v>
+        <v>708</v>
       </c>
       <c r="L9" t="n">
-        <v>659.8</v>
+        <v>676.3</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>823</v>
+        <v>805</v>
       </c>
       <c r="C10" t="n">
-        <v>747</v>
+        <v>778</v>
       </c>
       <c r="D10" t="n">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="E10" t="n">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="F10" t="n">
-        <v>714</v>
+        <v>733</v>
       </c>
       <c r="G10" t="n">
-        <v>805</v>
+        <v>766</v>
       </c>
       <c r="H10" t="n">
-        <v>776</v>
+        <v>737</v>
       </c>
       <c r="I10" t="n">
-        <v>908</v>
+        <v>732</v>
       </c>
       <c r="J10" t="n">
-        <v>785</v>
+        <v>865</v>
       </c>
       <c r="K10" t="n">
-        <v>847</v>
+        <v>810</v>
       </c>
       <c r="L10" t="n">
-        <v>791.9</v>
+        <v>772</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="C11" t="n">
-        <v>748</v>
+        <v>912</v>
       </c>
       <c r="D11" t="n">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="E11" t="n">
-        <v>852</v>
+        <v>739</v>
       </c>
       <c r="F11" t="n">
-        <v>677</v>
+        <v>785</v>
       </c>
       <c r="G11" t="n">
-        <v>701</v>
+        <v>816</v>
       </c>
       <c r="H11" t="n">
-        <v>733</v>
+        <v>708</v>
       </c>
       <c r="I11" t="n">
-        <v>722</v>
+        <v>675</v>
       </c>
       <c r="J11" t="n">
-        <v>718</v>
+        <v>780</v>
       </c>
       <c r="K11" t="n">
-        <v>785</v>
+        <v>740</v>
       </c>
       <c r="L11" t="n">
-        <v>748.3</v>
+        <v>765.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>605</v>
+        <v>656</v>
       </c>
       <c r="C12" t="n">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="D12" t="n">
-        <v>675</v>
+        <v>643</v>
       </c>
       <c r="E12" t="n">
-        <v>827</v>
+        <v>588</v>
       </c>
       <c r="F12" t="n">
-        <v>629</v>
+        <v>689</v>
       </c>
       <c r="G12" t="n">
-        <v>677</v>
+        <v>696</v>
       </c>
       <c r="H12" t="n">
-        <v>648</v>
+        <v>680</v>
       </c>
       <c r="I12" t="n">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="J12" t="n">
-        <v>673</v>
+        <v>689</v>
       </c>
       <c r="K12" t="n">
-        <v>745</v>
+        <v>665</v>
       </c>
       <c r="L12" t="n">
-        <v>685.2</v>
+        <v>667.9</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>636</v>
+        <v>571</v>
       </c>
       <c r="C13" t="n">
-        <v>630</v>
+        <v>590</v>
       </c>
       <c r="D13" t="n">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="E13" t="n">
-        <v>622</v>
+        <v>607</v>
       </c>
       <c r="F13" t="n">
-        <v>630</v>
+        <v>589</v>
       </c>
       <c r="G13" t="n">
-        <v>559</v>
+        <v>632</v>
       </c>
       <c r="H13" t="n">
-        <v>522</v>
+        <v>601</v>
       </c>
       <c r="I13" t="n">
-        <v>572</v>
+        <v>650</v>
       </c>
       <c r="J13" t="n">
-        <v>561</v>
+        <v>686</v>
       </c>
       <c r="K13" t="n">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="L13" t="n">
-        <v>590.2</v>
+        <v>612</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>625</v>
+        <v>647</v>
       </c>
       <c r="C14" t="n">
-        <v>658</v>
+        <v>629</v>
       </c>
       <c r="D14" t="n">
-        <v>601</v>
+        <v>536</v>
       </c>
       <c r="E14" t="n">
-        <v>742</v>
+        <v>650</v>
       </c>
       <c r="F14" t="n">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="G14" t="n">
-        <v>621</v>
+        <v>588</v>
       </c>
       <c r="H14" t="n">
-        <v>580</v>
+        <v>706</v>
       </c>
       <c r="I14" t="n">
-        <v>686</v>
+        <v>582</v>
       </c>
       <c r="J14" t="n">
-        <v>630</v>
+        <v>764</v>
       </c>
       <c r="K14" t="n">
         <v>644</v>
       </c>
       <c r="L14" t="n">
-        <v>638.8</v>
+        <v>632.2</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="C15" t="n">
-        <v>662</v>
+        <v>704</v>
       </c>
       <c r="D15" t="n">
-        <v>703</v>
+        <v>683</v>
       </c>
       <c r="E15" t="n">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="F15" t="n">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="G15" t="n">
+        <v>683</v>
+      </c>
+      <c r="H15" t="n">
         <v>673</v>
       </c>
-      <c r="H15" t="n">
-        <v>749</v>
-      </c>
       <c r="I15" t="n">
-        <v>675</v>
+        <v>701</v>
       </c>
       <c r="J15" t="n">
-        <v>652</v>
+        <v>751</v>
       </c>
       <c r="K15" t="n">
-        <v>664</v>
+        <v>765</v>
       </c>
       <c r="L15" t="n">
-        <v>683.5</v>
+        <v>701.7</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="C16" t="n">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="D16" t="n">
-        <v>714</v>
+        <v>669</v>
       </c>
       <c r="E16" t="n">
         <v>689</v>
       </c>
       <c r="F16" t="n">
-        <v>720</v>
+        <v>638</v>
       </c>
       <c r="G16" t="n">
-        <v>671</v>
+        <v>646</v>
       </c>
       <c r="H16" t="n">
-        <v>700</v>
+        <v>676</v>
       </c>
       <c r="I16" t="n">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="J16" t="n">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="K16" t="n">
-        <v>710</v>
+        <v>767</v>
       </c>
       <c r="L16" t="n">
-        <v>696.9</v>
+        <v>677.5</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>794</v>
+        <v>862</v>
       </c>
       <c r="C17" t="n">
-        <v>818</v>
+        <v>862</v>
       </c>
       <c r="D17" t="n">
-        <v>824</v>
+        <v>788</v>
       </c>
       <c r="E17" t="n">
-        <v>834</v>
+        <v>692</v>
       </c>
       <c r="F17" t="n">
-        <v>878</v>
+        <v>845</v>
       </c>
       <c r="G17" t="n">
-        <v>897</v>
+        <v>841</v>
       </c>
       <c r="H17" t="n">
-        <v>936</v>
+        <v>774</v>
       </c>
       <c r="I17" t="n">
-        <v>862</v>
+        <v>800</v>
       </c>
       <c r="J17" t="n">
-        <v>799</v>
+        <v>730</v>
       </c>
       <c r="K17" t="n">
-        <v>811</v>
+        <v>825</v>
       </c>
       <c r="L17" t="n">
-        <v>845.3</v>
+        <v>801.9</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>635</v>
+        <v>676</v>
       </c>
       <c r="C18" t="n">
-        <v>607</v>
+        <v>680</v>
       </c>
       <c r="D18" t="n">
-        <v>694</v>
+        <v>662</v>
       </c>
       <c r="E18" t="n">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="F18" t="n">
-        <v>667</v>
+        <v>621</v>
       </c>
       <c r="G18" t="n">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="H18" t="n">
-        <v>655</v>
+        <v>757</v>
       </c>
       <c r="I18" t="n">
-        <v>735</v>
+        <v>601</v>
       </c>
       <c r="J18" t="n">
-        <v>674</v>
+        <v>679</v>
       </c>
       <c r="K18" t="n">
-        <v>661</v>
+        <v>696</v>
       </c>
       <c r="L18" t="n">
-        <v>661.2</v>
+        <v>666.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>725</v>
+        <v>771</v>
       </c>
       <c r="C19" t="n">
-        <v>661</v>
+        <v>713</v>
       </c>
       <c r="D19" t="n">
-        <v>742</v>
+        <v>705</v>
       </c>
       <c r="E19" t="n">
-        <v>721</v>
+        <v>694</v>
       </c>
       <c r="F19" t="n">
-        <v>685</v>
+        <v>652</v>
       </c>
       <c r="G19" t="n">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="H19" t="n">
-        <v>644</v>
+        <v>687</v>
       </c>
       <c r="I19" t="n">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="J19" t="n">
-        <v>640</v>
+        <v>698</v>
       </c>
       <c r="K19" t="n">
-        <v>599</v>
+        <v>744</v>
       </c>
       <c r="L19" t="n">
-        <v>678.4</v>
+        <v>705.4</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>751</v>
+        <v>639</v>
       </c>
       <c r="C20" t="n">
-        <v>735</v>
+        <v>698</v>
       </c>
       <c r="D20" t="n">
-        <v>729</v>
+        <v>623</v>
       </c>
       <c r="E20" t="n">
-        <v>668</v>
+        <v>616</v>
       </c>
       <c r="F20" t="n">
-        <v>655</v>
+        <v>806</v>
       </c>
       <c r="G20" t="n">
-        <v>696</v>
+        <v>777</v>
       </c>
       <c r="H20" t="n">
-        <v>579</v>
+        <v>747</v>
       </c>
       <c r="I20" t="n">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="J20" t="n">
-        <v>717</v>
+        <v>686</v>
       </c>
       <c r="K20" t="n">
-        <v>713</v>
+        <v>617</v>
       </c>
       <c r="L20" t="n">
-        <v>687.2</v>
+        <v>684.2</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>662</v>
+        <v>691</v>
       </c>
       <c r="C21" t="n">
-        <v>703</v>
+        <v>730</v>
       </c>
       <c r="D21" t="n">
-        <v>634</v>
+        <v>715</v>
       </c>
       <c r="E21" t="n">
-        <v>647</v>
+        <v>766</v>
       </c>
       <c r="F21" t="n">
-        <v>663</v>
+        <v>625</v>
       </c>
       <c r="G21" t="n">
-        <v>636</v>
+        <v>721</v>
       </c>
       <c r="H21" t="n">
-        <v>758</v>
+        <v>745</v>
       </c>
       <c r="I21" t="n">
-        <v>728</v>
+        <v>768</v>
       </c>
       <c r="J21" t="n">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="K21" t="n">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="L21" t="n">
-        <v>672.8</v>
+        <v>703.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
+        <v>719</v>
+      </c>
+      <c r="C22" t="n">
+        <v>619</v>
+      </c>
+      <c r="D22" t="n">
+        <v>635</v>
+      </c>
+      <c r="E22" t="n">
+        <v>646</v>
+      </c>
+      <c r="F22" t="n">
         <v>624</v>
       </c>
-      <c r="C22" t="n">
-        <v>615</v>
-      </c>
-      <c r="D22" t="n">
-        <v>634</v>
-      </c>
-      <c r="E22" t="n">
-        <v>678</v>
-      </c>
-      <c r="F22" t="n">
-        <v>619</v>
-      </c>
       <c r="G22" t="n">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="H22" t="n">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="I22" t="n">
-        <v>582</v>
+        <v>668</v>
       </c>
       <c r="J22" t="n">
-        <v>584</v>
+        <v>635</v>
       </c>
       <c r="K22" t="n">
-        <v>715</v>
+        <v>664</v>
       </c>
       <c r="L22" t="n">
-        <v>631.9</v>
+        <v>649.2</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>739</v>
+        <v>814</v>
       </c>
       <c r="C23" t="n">
-        <v>695</v>
+        <v>773</v>
       </c>
       <c r="D23" t="n">
+        <v>766</v>
+      </c>
+      <c r="E23" t="n">
+        <v>788</v>
+      </c>
+      <c r="F23" t="n">
+        <v>737</v>
+      </c>
+      <c r="G23" t="n">
+        <v>904</v>
+      </c>
+      <c r="H23" t="n">
+        <v>837</v>
+      </c>
+      <c r="I23" t="n">
+        <v>692</v>
+      </c>
+      <c r="J23" t="n">
         <v>809</v>
       </c>
-      <c r="E23" t="n">
-        <v>794</v>
-      </c>
-      <c r="F23" t="n">
-        <v>836</v>
-      </c>
-      <c r="G23" t="n">
-        <v>773</v>
-      </c>
-      <c r="H23" t="n">
-        <v>655</v>
-      </c>
-      <c r="I23" t="n">
-        <v>768</v>
-      </c>
-      <c r="J23" t="n">
-        <v>805</v>
-      </c>
       <c r="K23" t="n">
-        <v>778</v>
+        <v>743</v>
       </c>
       <c r="L23" t="n">
-        <v>765.2</v>
+        <v>786.3</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="C24" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="D24" t="n">
-        <v>730</v>
+        <v>660</v>
       </c>
       <c r="E24" t="n">
-        <v>675</v>
+        <v>781</v>
       </c>
       <c r="F24" t="n">
-        <v>728</v>
+        <v>659</v>
       </c>
       <c r="G24" t="n">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="H24" t="n">
-        <v>640</v>
+        <v>737</v>
       </c>
       <c r="I24" t="n">
-        <v>715</v>
+        <v>623</v>
       </c>
       <c r="J24" t="n">
-        <v>719</v>
+        <v>789</v>
       </c>
       <c r="K24" t="n">
-        <v>651</v>
+        <v>616</v>
       </c>
       <c r="L24" t="n">
-        <v>686.8</v>
+        <v>693.2</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="C25" t="n">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="D25" t="n">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="E25" t="n">
-        <v>706</v>
+        <v>751</v>
       </c>
       <c r="F25" t="n">
-        <v>653</v>
+        <v>612</v>
       </c>
       <c r="G25" t="n">
-        <v>741</v>
+        <v>777</v>
       </c>
       <c r="H25" t="n">
-        <v>751</v>
+        <v>649</v>
       </c>
       <c r="I25" t="n">
+        <v>674</v>
+      </c>
+      <c r="J25" t="n">
         <v>639</v>
       </c>
-      <c r="J25" t="n">
-        <v>660</v>
-      </c>
       <c r="K25" t="n">
-        <v>694</v>
+        <v>750</v>
       </c>
       <c r="L25" t="n">
-        <v>676.5</v>
+        <v>674</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>769</v>
+        <v>833</v>
       </c>
       <c r="C26" t="n">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="D26" t="n">
-        <v>734</v>
+        <v>790</v>
       </c>
       <c r="E26" t="n">
-        <v>833</v>
+        <v>788</v>
       </c>
       <c r="F26" t="n">
-        <v>778</v>
+        <v>762</v>
       </c>
       <c r="G26" t="n">
-        <v>662</v>
+        <v>768</v>
       </c>
       <c r="H26" t="n">
-        <v>772</v>
+        <v>710</v>
       </c>
       <c r="I26" t="n">
-        <v>752</v>
+        <v>824</v>
       </c>
       <c r="J26" t="n">
-        <v>751</v>
+        <v>708</v>
       </c>
       <c r="K26" t="n">
-        <v>786</v>
+        <v>680</v>
       </c>
       <c r="L26" t="n">
-        <v>758.5</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>836</v>
+        <v>747</v>
       </c>
       <c r="C27" t="n">
-        <v>738</v>
+        <v>755</v>
       </c>
       <c r="D27" t="n">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="E27" t="n">
-        <v>712</v>
+        <v>849</v>
       </c>
       <c r="F27" t="n">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="G27" t="n">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="H27" t="n">
-        <v>687</v>
+        <v>750</v>
       </c>
       <c r="I27" t="n">
-        <v>778</v>
+        <v>740</v>
       </c>
       <c r="J27" t="n">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="K27" t="n">
-        <v>743</v>
+        <v>711</v>
       </c>
       <c r="L27" t="n">
-        <v>761.1</v>
+        <v>766.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>631</v>
+        <v>583</v>
       </c>
       <c r="C28" t="n">
-        <v>592</v>
+        <v>661</v>
       </c>
       <c r="D28" t="n">
-        <v>628</v>
+        <v>603</v>
       </c>
       <c r="E28" t="n">
-        <v>651</v>
+        <v>677</v>
       </c>
       <c r="F28" t="n">
-        <v>564</v>
+        <v>589</v>
       </c>
       <c r="G28" t="n">
-        <v>621</v>
+        <v>649</v>
       </c>
       <c r="H28" t="n">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="I28" t="n">
-        <v>613</v>
+        <v>565</v>
       </c>
       <c r="J28" t="n">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="K28" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L28" t="n">
-        <v>615.8</v>
+        <v>627.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>730</v>
+        <v>753</v>
       </c>
       <c r="C29" t="n">
-        <v>682</v>
+        <v>633</v>
       </c>
       <c r="D29" t="n">
-        <v>878</v>
+        <v>654</v>
       </c>
       <c r="E29" t="n">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="F29" t="n">
-        <v>778</v>
+        <v>839</v>
       </c>
       <c r="G29" t="n">
-        <v>853</v>
+        <v>773</v>
       </c>
       <c r="H29" t="n">
-        <v>780</v>
+        <v>652</v>
       </c>
       <c r="I29" t="n">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="J29" t="n">
-        <v>686</v>
+        <v>727</v>
       </c>
       <c r="K29" t="n">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="L29" t="n">
-        <v>744.9</v>
+        <v>713.9</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>650</v>
+        <v>694</v>
       </c>
       <c r="C30" t="n">
-        <v>653</v>
+        <v>672</v>
       </c>
       <c r="D30" t="n">
-        <v>725</v>
+        <v>590</v>
       </c>
       <c r="E30" t="n">
-        <v>693</v>
+        <v>681</v>
       </c>
       <c r="F30" t="n">
-        <v>733</v>
+        <v>680</v>
       </c>
       <c r="G30" t="n">
-        <v>631</v>
+        <v>654</v>
       </c>
       <c r="H30" t="n">
-        <v>655</v>
+        <v>763</v>
       </c>
       <c r="I30" t="n">
-        <v>679</v>
+        <v>835</v>
       </c>
       <c r="J30" t="n">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="K30" t="n">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="L30" t="n">
-        <v>673.9</v>
+        <v>690.8</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>715</v>
+        <v>608</v>
       </c>
       <c r="C31" t="n">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="D31" t="n">
-        <v>720</v>
+        <v>666</v>
       </c>
       <c r="E31" t="n">
-        <v>718</v>
+        <v>676</v>
       </c>
       <c r="F31" t="n">
         <v>687</v>
       </c>
       <c r="G31" t="n">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="H31" t="n">
-        <v>686</v>
+        <v>636</v>
       </c>
       <c r="I31" t="n">
-        <v>676</v>
+        <v>651</v>
       </c>
       <c r="J31" t="n">
-        <v>725</v>
+        <v>621</v>
       </c>
       <c r="K31" t="n">
-        <v>646</v>
+        <v>711</v>
       </c>
       <c r="L31" t="n">
-        <v>694</v>
+        <v>661</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>617</v>
+        <v>685</v>
       </c>
       <c r="C32" t="n">
-        <v>668</v>
+        <v>601</v>
       </c>
       <c r="D32" t="n">
-        <v>546</v>
+        <v>606</v>
       </c>
       <c r="E32" t="n">
-        <v>634</v>
+        <v>726</v>
       </c>
       <c r="F32" t="n">
-        <v>657</v>
+        <v>741</v>
       </c>
       <c r="G32" t="n">
-        <v>635</v>
+        <v>729</v>
       </c>
       <c r="H32" t="n">
-        <v>621</v>
+        <v>652</v>
       </c>
       <c r="I32" t="n">
-        <v>637</v>
+        <v>538</v>
       </c>
       <c r="J32" t="n">
-        <v>636</v>
+        <v>604</v>
       </c>
       <c r="K32" t="n">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="L32" t="n">
-        <v>634.1</v>
+        <v>661.1</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>856</v>
+        <v>689</v>
       </c>
       <c r="C33" t="n">
-        <v>874</v>
+        <v>745</v>
       </c>
       <c r="D33" t="n">
-        <v>772</v>
+        <v>718</v>
       </c>
       <c r="E33" t="n">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="F33" t="n">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="G33" t="n">
-        <v>738</v>
+        <v>723</v>
       </c>
       <c r="H33" t="n">
-        <v>800</v>
+        <v>733</v>
       </c>
       <c r="I33" t="n">
-        <v>641</v>
+        <v>812</v>
       </c>
       <c r="J33" t="n">
-        <v>768</v>
+        <v>702</v>
       </c>
       <c r="K33" t="n">
-        <v>720</v>
+        <v>783</v>
       </c>
       <c r="L33" t="n">
-        <v>753.6</v>
+        <v>730.1</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>590</v>
+        <v>683</v>
       </c>
       <c r="C34" t="n">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="D34" t="n">
-        <v>638</v>
+        <v>765</v>
       </c>
       <c r="E34" t="n">
-        <v>632</v>
+        <v>732</v>
       </c>
       <c r="F34" t="n">
-        <v>677</v>
+        <v>616</v>
       </c>
       <c r="G34" t="n">
-        <v>624</v>
+        <v>670</v>
       </c>
       <c r="H34" t="n">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="I34" t="n">
-        <v>668</v>
+        <v>608</v>
       </c>
       <c r="J34" t="n">
-        <v>620</v>
+        <v>784</v>
       </c>
       <c r="K34" t="n">
-        <v>638</v>
+        <v>588</v>
       </c>
       <c r="L34" t="n">
-        <v>631.8</v>
+        <v>665.6</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C35" t="n">
-        <v>800</v>
+        <v>846</v>
       </c>
       <c r="D35" t="n">
-        <v>864</v>
+        <v>784</v>
       </c>
       <c r="E35" t="n">
-        <v>744</v>
+        <v>817</v>
       </c>
       <c r="F35" t="n">
-        <v>857</v>
+        <v>829</v>
       </c>
       <c r="G35" t="n">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="H35" t="n">
-        <v>717</v>
+        <v>811</v>
       </c>
       <c r="I35" t="n">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="J35" t="n">
-        <v>730</v>
+        <v>754</v>
       </c>
       <c r="K35" t="n">
-        <v>775</v>
+        <v>797</v>
       </c>
       <c r="L35" t="n">
-        <v>768.5</v>
+        <v>782.9</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>587</v>
+        <v>523</v>
       </c>
       <c r="C36" t="n">
-        <v>567</v>
+        <v>630</v>
       </c>
       <c r="D36" t="n">
-        <v>698</v>
+        <v>612</v>
       </c>
       <c r="E36" t="n">
-        <v>554</v>
+        <v>643</v>
       </c>
       <c r="F36" t="n">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="G36" t="n">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="H36" t="n">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="I36" t="n">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="J36" t="n">
-        <v>626</v>
+        <v>568</v>
       </c>
       <c r="K36" t="n">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="L36" t="n">
-        <v>592.2</v>
+        <v>594.1</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>607</v>
+        <v>635</v>
       </c>
       <c r="C37" t="n">
-        <v>649</v>
+        <v>755</v>
       </c>
       <c r="D37" t="n">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="E37" t="n">
-        <v>732</v>
+        <v>647</v>
       </c>
       <c r="F37" t="n">
-        <v>648</v>
+        <v>699</v>
       </c>
       <c r="G37" t="n">
-        <v>736</v>
+        <v>655</v>
       </c>
       <c r="H37" t="n">
-        <v>575</v>
+        <v>665</v>
       </c>
       <c r="I37" t="n">
-        <v>652</v>
+        <v>691</v>
       </c>
       <c r="J37" t="n">
-        <v>613</v>
+        <v>767</v>
       </c>
       <c r="K37" t="n">
-        <v>654</v>
+        <v>726</v>
       </c>
       <c r="L37" t="n">
-        <v>657.9</v>
+        <v>695.9</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>722</v>
+        <v>675</v>
       </c>
       <c r="C38" t="n">
-        <v>823</v>
+        <v>687</v>
       </c>
       <c r="D38" t="n">
-        <v>705</v>
+        <v>630</v>
       </c>
       <c r="E38" t="n">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="F38" t="n">
-        <v>721</v>
+        <v>673</v>
       </c>
       <c r="G38" t="n">
-        <v>776</v>
+        <v>753</v>
       </c>
       <c r="H38" t="n">
-        <v>691</v>
+        <v>757</v>
       </c>
       <c r="I38" t="n">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="J38" t="n">
-        <v>707</v>
+        <v>752</v>
       </c>
       <c r="K38" t="n">
-        <v>857</v>
+        <v>696</v>
       </c>
       <c r="L38" t="n">
-        <v>747.3</v>
+        <v>707.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="C39" t="n">
+        <v>600</v>
+      </c>
+      <c r="D39" t="n">
+        <v>567</v>
+      </c>
+      <c r="E39" t="n">
+        <v>697</v>
+      </c>
+      <c r="F39" t="n">
         <v>533</v>
       </c>
-      <c r="D39" t="n">
-        <v>687</v>
-      </c>
-      <c r="E39" t="n">
-        <v>655</v>
-      </c>
-      <c r="F39" t="n">
-        <v>580</v>
-      </c>
       <c r="G39" t="n">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="H39" t="n">
-        <v>523</v>
+        <v>624</v>
       </c>
       <c r="I39" t="n">
-        <v>582</v>
+        <v>708</v>
       </c>
       <c r="J39" t="n">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="K39" t="n">
-        <v>574</v>
+        <v>638</v>
       </c>
       <c r="L39" t="n">
-        <v>593.6</v>
+        <v>617.7</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>752</v>
+        <v>726</v>
       </c>
       <c r="C40" t="n">
-        <v>767</v>
+        <v>666</v>
       </c>
       <c r="D40" t="n">
-        <v>760</v>
+        <v>740</v>
       </c>
       <c r="E40" t="n">
-        <v>746</v>
+        <v>696</v>
       </c>
       <c r="F40" t="n">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="G40" t="n">
-        <v>693</v>
+        <v>784</v>
       </c>
       <c r="H40" t="n">
-        <v>745</v>
+        <v>703</v>
       </c>
       <c r="I40" t="n">
         <v>772</v>
       </c>
       <c r="J40" t="n">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="K40" t="n">
-        <v>816</v>
+        <v>694</v>
       </c>
       <c r="L40" t="n">
-        <v>749.5</v>
+        <v>723.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>664</v>
+        <v>609</v>
       </c>
       <c r="C41" t="n">
-        <v>650</v>
+        <v>701</v>
       </c>
       <c r="D41" t="n">
-        <v>721</v>
+        <v>600</v>
       </c>
       <c r="E41" t="n">
-        <v>634</v>
+        <v>709</v>
       </c>
       <c r="F41" t="n">
-        <v>681</v>
+        <v>610</v>
       </c>
       <c r="G41" t="n">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="H41" t="n">
-        <v>726</v>
+        <v>628</v>
       </c>
       <c r="I41" t="n">
-        <v>708</v>
+        <v>668</v>
       </c>
       <c r="J41" t="n">
-        <v>743</v>
+        <v>645</v>
       </c>
       <c r="K41" t="n">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="L41" t="n">
-        <v>680.5</v>
+        <v>644.3</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="C42" t="n">
-        <v>574</v>
+        <v>724</v>
       </c>
       <c r="D42" t="n">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E42" t="n">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="F42" t="n">
-        <v>581</v>
+        <v>634</v>
       </c>
       <c r="G42" t="n">
-        <v>630</v>
+        <v>607</v>
       </c>
       <c r="H42" t="n">
-        <v>607</v>
+        <v>650</v>
       </c>
       <c r="I42" t="n">
-        <v>644</v>
+        <v>616</v>
       </c>
       <c r="J42" t="n">
-        <v>566</v>
+        <v>627</v>
       </c>
       <c r="K42" t="n">
-        <v>667</v>
+        <v>643</v>
       </c>
       <c r="L42" t="n">
-        <v>615.2</v>
+        <v>639.2</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>736</v>
+        <v>774</v>
       </c>
       <c r="C43" t="n">
-        <v>743</v>
+        <v>682</v>
       </c>
       <c r="D43" t="n">
-        <v>854</v>
+        <v>721</v>
       </c>
       <c r="E43" t="n">
-        <v>815</v>
+        <v>762</v>
       </c>
       <c r="F43" t="n">
-        <v>725</v>
+        <v>779</v>
       </c>
       <c r="G43" t="n">
-        <v>703</v>
+        <v>768</v>
       </c>
       <c r="H43" t="n">
-        <v>756</v>
+        <v>792</v>
       </c>
       <c r="I43" t="n">
-        <v>709</v>
+        <v>745</v>
       </c>
       <c r="J43" t="n">
-        <v>863</v>
+        <v>647</v>
       </c>
       <c r="K43" t="n">
-        <v>702</v>
+        <v>787</v>
       </c>
       <c r="L43" t="n">
-        <v>760.6</v>
+        <v>745.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>757</v>
+        <v>779</v>
       </c>
       <c r="C44" t="n">
-        <v>725</v>
+        <v>744</v>
       </c>
       <c r="D44" t="n">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="E44" t="n">
-        <v>750</v>
+        <v>823</v>
       </c>
       <c r="F44" t="n">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="G44" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H44" t="n">
-        <v>654</v>
+        <v>742</v>
       </c>
       <c r="I44" t="n">
-        <v>799</v>
+        <v>732</v>
       </c>
       <c r="J44" t="n">
-        <v>772</v>
+        <v>714</v>
       </c>
       <c r="K44" t="n">
         <v>793</v>
       </c>
       <c r="L44" t="n">
-        <v>743.4</v>
+        <v>754</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>669</v>
+        <v>594</v>
       </c>
       <c r="C45" t="n">
-        <v>588</v>
+        <v>743</v>
       </c>
       <c r="D45" t="n">
-        <v>586</v>
+        <v>697</v>
       </c>
       <c r="E45" t="n">
-        <v>705</v>
+        <v>608</v>
       </c>
       <c r="F45" t="n">
+        <v>620</v>
+      </c>
+      <c r="G45" t="n">
+        <v>606</v>
+      </c>
+      <c r="H45" t="n">
         <v>635</v>
       </c>
-      <c r="G45" t="n">
-        <v>622</v>
-      </c>
-      <c r="H45" t="n">
-        <v>706</v>
-      </c>
       <c r="I45" t="n">
-        <v>605</v>
+        <v>560</v>
       </c>
       <c r="J45" t="n">
-        <v>699</v>
+        <v>647</v>
       </c>
       <c r="K45" t="n">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="L45" t="n">
-        <v>643.8</v>
+        <v>632.9</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>728</v>
+        <v>627</v>
       </c>
       <c r="C46" t="n">
-        <v>694</v>
+        <v>576</v>
       </c>
       <c r="D46" t="n">
-        <v>665</v>
+        <v>597</v>
       </c>
       <c r="E46" t="n">
-        <v>671</v>
+        <v>630</v>
       </c>
       <c r="F46" t="n">
-        <v>673</v>
+        <v>661</v>
       </c>
       <c r="G46" t="n">
-        <v>658</v>
+        <v>731</v>
       </c>
       <c r="H46" t="n">
-        <v>647</v>
+        <v>623</v>
       </c>
       <c r="I46" t="n">
-        <v>653</v>
+        <v>760</v>
       </c>
       <c r="J46" t="n">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="K46" t="n">
-        <v>604</v>
+        <v>734</v>
       </c>
       <c r="L46" t="n">
-        <v>661.2</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>738</v>
+        <v>632</v>
       </c>
       <c r="C47" t="n">
-        <v>757</v>
+        <v>710</v>
       </c>
       <c r="D47" t="n">
-        <v>772</v>
+        <v>696</v>
       </c>
       <c r="E47" t="n">
-        <v>726</v>
+        <v>802</v>
       </c>
       <c r="F47" t="n">
-        <v>752</v>
+        <v>715</v>
       </c>
       <c r="G47" t="n">
-        <v>793</v>
+        <v>652</v>
       </c>
       <c r="H47" t="n">
-        <v>881</v>
+        <v>731</v>
       </c>
       <c r="I47" t="n">
-        <v>854</v>
+        <v>685</v>
       </c>
       <c r="J47" t="n">
-        <v>758</v>
+        <v>713</v>
       </c>
       <c r="K47" t="n">
-        <v>715</v>
+        <v>751</v>
       </c>
       <c r="L47" t="n">
-        <v>774.6</v>
+        <v>708.7</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>609</v>
+        <v>668</v>
       </c>
       <c r="C48" t="n">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="D48" t="n">
-        <v>674</v>
+        <v>600</v>
       </c>
       <c r="E48" t="n">
-        <v>686</v>
+        <v>772</v>
       </c>
       <c r="F48" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G48" t="n">
-        <v>749</v>
+        <v>643</v>
       </c>
       <c r="H48" t="n">
-        <v>649</v>
+        <v>699</v>
       </c>
       <c r="I48" t="n">
-        <v>644</v>
+        <v>610</v>
       </c>
       <c r="J48" t="n">
-        <v>651</v>
+        <v>564</v>
       </c>
       <c r="K48" t="n">
-        <v>682</v>
+        <v>658</v>
       </c>
       <c r="L48" t="n">
-        <v>666.7</v>
+        <v>651.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>798</v>
+        <v>878</v>
       </c>
       <c r="C49" t="n">
-        <v>662</v>
+        <v>921</v>
       </c>
       <c r="D49" t="n">
-        <v>832</v>
+        <v>710</v>
       </c>
       <c r="E49" t="n">
-        <v>799</v>
+        <v>711</v>
       </c>
       <c r="F49" t="n">
-        <v>785</v>
+        <v>847</v>
       </c>
       <c r="G49" t="n">
-        <v>821</v>
+        <v>843</v>
       </c>
       <c r="H49" t="n">
-        <v>815</v>
+        <v>726</v>
       </c>
       <c r="I49" t="n">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="J49" t="n">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="K49" t="n">
-        <v>826</v>
+        <v>810</v>
       </c>
       <c r="L49" t="n">
-        <v>782.3</v>
+        <v>792.7</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>640</v>
+        <v>608</v>
       </c>
       <c r="C50" t="n">
+        <v>603</v>
+      </c>
+      <c r="D50" t="n">
+        <v>630</v>
+      </c>
+      <c r="E50" t="n">
+        <v>598</v>
+      </c>
+      <c r="F50" t="n">
+        <v>662</v>
+      </c>
+      <c r="G50" t="n">
+        <v>618</v>
+      </c>
+      <c r="H50" t="n">
+        <v>612</v>
+      </c>
+      <c r="I50" t="n">
         <v>703</v>
       </c>
-      <c r="D50" t="n">
-        <v>691</v>
-      </c>
-      <c r="E50" t="n">
-        <v>587</v>
-      </c>
-      <c r="F50" t="n">
-        <v>582</v>
-      </c>
-      <c r="G50" t="n">
-        <v>653</v>
-      </c>
-      <c r="H50" t="n">
-        <v>581</v>
-      </c>
-      <c r="I50" t="n">
-        <v>601</v>
-      </c>
       <c r="J50" t="n">
-        <v>605</v>
+        <v>639</v>
       </c>
       <c r="K50" t="n">
-        <v>685</v>
+        <v>659</v>
       </c>
       <c r="L50" t="n">
-        <v>632.8</v>
+        <v>633.2</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>677</v>
+        <v>814</v>
       </c>
       <c r="C51" t="n">
-        <v>611</v>
+        <v>707</v>
       </c>
       <c r="D51" t="n">
-        <v>722</v>
+        <v>652</v>
       </c>
       <c r="E51" t="n">
-        <v>849</v>
+        <v>685</v>
       </c>
       <c r="F51" t="n">
-        <v>666</v>
+        <v>726</v>
       </c>
       <c r="G51" t="n">
-        <v>711</v>
+        <v>672</v>
       </c>
       <c r="H51" t="n">
-        <v>686</v>
+        <v>631</v>
       </c>
       <c r="I51" t="n">
-        <v>703</v>
+        <v>675</v>
       </c>
       <c r="J51" t="n">
-        <v>608</v>
+        <v>684</v>
       </c>
       <c r="K51" t="n">
-        <v>674</v>
+        <v>654</v>
       </c>
       <c r="L51" t="n">
-        <v>690.7</v>
+        <v>690</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>688.78</v>
+        <v>691.48</v>
       </c>
       <c r="C52" t="n">
-        <v>684.5</v>
+        <v>705.02</v>
       </c>
       <c r="D52" t="n">
-        <v>710.26</v>
+        <v>678.28</v>
       </c>
       <c r="E52" t="n">
-        <v>712</v>
+        <v>712.04</v>
       </c>
       <c r="F52" t="n">
-        <v>693.66</v>
+        <v>694.98</v>
       </c>
       <c r="G52" t="n">
-        <v>697.3200000000001</v>
+        <v>703.84</v>
       </c>
       <c r="H52" t="n">
-        <v>688.7</v>
+        <v>704.08</v>
       </c>
       <c r="I52" t="n">
-        <v>691.96</v>
+        <v>689.84</v>
       </c>
       <c r="J52" t="n">
-        <v>689.3</v>
+        <v>702.48</v>
       </c>
       <c r="K52" t="n">
-        <v>700.48</v>
+        <v>711.08</v>
       </c>
       <c r="L52" t="n">
-        <v>695.696</v>
+        <v>699.3119999999998</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.11841869354248</v>
+        <v>4.64755916595459</v>
       </c>
       <c r="C2" t="n">
-        <v>4.599212169647217</v>
+        <v>4.510789632797241</v>
       </c>
       <c r="D2" t="n">
-        <v>4.336841583251953</v>
+        <v>4.30075478553772</v>
       </c>
       <c r="E2" t="n">
-        <v>4.397225856781006</v>
+        <v>4.700557708740234</v>
       </c>
       <c r="F2" t="n">
-        <v>6.19123387336731</v>
+        <v>4.806395769119263</v>
       </c>
       <c r="G2" t="n">
-        <v>4.752596855163574</v>
+        <v>4.679089307785034</v>
       </c>
       <c r="H2" t="n">
-        <v>4.441331624984741</v>
+        <v>4.694669485092163</v>
       </c>
       <c r="I2" t="n">
-        <v>4.361688852310181</v>
+        <v>4.288782596588135</v>
       </c>
       <c r="J2" t="n">
-        <v>4.278633594512939</v>
+        <v>4.307390451431274</v>
       </c>
       <c r="K2" t="n">
-        <v>4.175705194473267</v>
+        <v>5.331000804901123</v>
       </c>
       <c r="L2" t="n">
-        <v>4.565288829803467</v>
+        <v>4.626698970794678</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.926405906677246</v>
+        <v>5.293358325958252</v>
       </c>
       <c r="C3" t="n">
-        <v>4.52486515045166</v>
+        <v>5.140804290771484</v>
       </c>
       <c r="D3" t="n">
-        <v>4.492887258529663</v>
+        <v>5.32532811164856</v>
       </c>
       <c r="E3" t="n">
-        <v>4.856828451156616</v>
+        <v>5.045104026794434</v>
       </c>
       <c r="F3" t="n">
-        <v>5.067002296447754</v>
+        <v>5.104440927505493</v>
       </c>
       <c r="G3" t="n">
-        <v>4.678280353546143</v>
+        <v>4.705313444137573</v>
       </c>
       <c r="H3" t="n">
-        <v>5.423689126968384</v>
+        <v>5.296696662902832</v>
       </c>
       <c r="I3" t="n">
-        <v>4.602718830108643</v>
+        <v>5.230623006820679</v>
       </c>
       <c r="J3" t="n">
-        <v>5.474087715148926</v>
+        <v>5.611611604690552</v>
       </c>
       <c r="K3" t="n">
-        <v>5.018719434738159</v>
+        <v>5.338393688201904</v>
       </c>
       <c r="L3" t="n">
-        <v>4.90654845237732</v>
+        <v>5.209167408943176</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.787329912185669</v>
+        <v>4.867903709411621</v>
       </c>
       <c r="C4" t="n">
-        <v>4.750292301177979</v>
+        <v>4.897370338439941</v>
       </c>
       <c r="D4" t="n">
-        <v>4.868902683258057</v>
+        <v>4.9373459815979</v>
       </c>
       <c r="E4" t="n">
-        <v>4.710988759994507</v>
+        <v>5.397580862045288</v>
       </c>
       <c r="F4" t="n">
-        <v>4.499809741973877</v>
+        <v>5.403295755386353</v>
       </c>
       <c r="G4" t="n">
-        <v>4.810567617416382</v>
+        <v>4.760369062423706</v>
       </c>
       <c r="H4" t="n">
-        <v>4.830656766891479</v>
+        <v>5.02619743347168</v>
       </c>
       <c r="I4" t="n">
-        <v>4.579667806625366</v>
+        <v>4.923717021942139</v>
       </c>
       <c r="J4" t="n">
-        <v>4.532295942306519</v>
+        <v>5.016684532165527</v>
       </c>
       <c r="K4" t="n">
-        <v>4.997698545455933</v>
+        <v>5.212560892105103</v>
       </c>
       <c r="L4" t="n">
-        <v>4.736821007728577</v>
+        <v>5.044302558898925</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.220680236816406</v>
+        <v>5.204423427581787</v>
       </c>
       <c r="C5" t="n">
-        <v>5.242409944534302</v>
+        <v>5.690164089202881</v>
       </c>
       <c r="D5" t="n">
-        <v>5.721483469009399</v>
+        <v>5.091058015823364</v>
       </c>
       <c r="E5" t="n">
-        <v>5.154436588287354</v>
+        <v>5.854960441589355</v>
       </c>
       <c r="F5" t="n">
-        <v>5.110532760620117</v>
+        <v>5.512420654296875</v>
       </c>
       <c r="G5" t="n">
-        <v>5.629886865615845</v>
+        <v>5.389953851699829</v>
       </c>
       <c r="H5" t="n">
-        <v>5.221447467803955</v>
+        <v>5.296683549880981</v>
       </c>
       <c r="I5" t="n">
-        <v>5.481411218643188</v>
+        <v>5.362896203994751</v>
       </c>
       <c r="J5" t="n">
-        <v>5.246152639389038</v>
+        <v>5.526000261306763</v>
       </c>
       <c r="K5" t="n">
-        <v>5.53011155128479</v>
+        <v>5.567079305648804</v>
       </c>
       <c r="L5" t="n">
-        <v>5.355855274200439</v>
+        <v>5.449563980102539</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.189934968948364</v>
+        <v>4.105036973953247</v>
       </c>
       <c r="C6" t="n">
-        <v>4.182992219924927</v>
+        <v>4.086895704269409</v>
       </c>
       <c r="D6" t="n">
-        <v>4.398366928100586</v>
+        <v>4.055675745010376</v>
       </c>
       <c r="E6" t="n">
-        <v>3.880440950393677</v>
+        <v>4.077958345413208</v>
       </c>
       <c r="F6" t="n">
-        <v>4.67774486541748</v>
+        <v>4.032531499862671</v>
       </c>
       <c r="G6" t="n">
-        <v>4.414115190505981</v>
+        <v>4.398033380508423</v>
       </c>
       <c r="H6" t="n">
-        <v>3.888888597488403</v>
+        <v>4.211516380310059</v>
       </c>
       <c r="I6" t="n">
-        <v>3.845963716506958</v>
+        <v>3.96480131149292</v>
       </c>
       <c r="J6" t="n">
-        <v>4.105868339538574</v>
+        <v>4.223623037338257</v>
       </c>
       <c r="K6" t="n">
-        <v>4.431229114532471</v>
+        <v>4.485289335250854</v>
       </c>
       <c r="L6" t="n">
-        <v>4.201554489135742</v>
+        <v>4.164136171340942</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.881731986999512</v>
+        <v>5.13044548034668</v>
       </c>
       <c r="C7" t="n">
-        <v>4.886553049087524</v>
+        <v>5.368699789047241</v>
       </c>
       <c r="D7" t="n">
-        <v>4.773185729980469</v>
+        <v>4.943984746932983</v>
       </c>
       <c r="E7" t="n">
-        <v>4.816679954528809</v>
+        <v>5.358558177947998</v>
       </c>
       <c r="F7" t="n">
-        <v>4.851838111877441</v>
+        <v>5.227080345153809</v>
       </c>
       <c r="G7" t="n">
-        <v>4.872850179672241</v>
+        <v>4.951910018920898</v>
       </c>
       <c r="H7" t="n">
-        <v>5.122040748596191</v>
+        <v>5.677038192749023</v>
       </c>
       <c r="I7" t="n">
-        <v>5.281026601791382</v>
+        <v>4.785576105117798</v>
       </c>
       <c r="J7" t="n">
-        <v>4.838299512863159</v>
+        <v>5.257006168365479</v>
       </c>
       <c r="K7" t="n">
-        <v>4.829668998718262</v>
+        <v>5.566319942474365</v>
       </c>
       <c r="L7" t="n">
-        <v>4.915387487411499</v>
+        <v>5.226661896705627</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.860761642456055</v>
+        <v>4.26575231552124</v>
       </c>
       <c r="C8" t="n">
-        <v>4.27229380607605</v>
+        <v>4.098830223083496</v>
       </c>
       <c r="D8" t="n">
-        <v>4.02382755279541</v>
+        <v>4.533252716064453</v>
       </c>
       <c r="E8" t="n">
-        <v>4.369652509689331</v>
+        <v>4.227387189865112</v>
       </c>
       <c r="F8" t="n">
-        <v>3.971977710723877</v>
+        <v>4.206806421279907</v>
       </c>
       <c r="G8" t="n">
-        <v>4.257741451263428</v>
+        <v>4.166903018951416</v>
       </c>
       <c r="H8" t="n">
-        <v>3.857018232345581</v>
+        <v>4.466076374053955</v>
       </c>
       <c r="I8" t="n">
-        <v>4.307456016540527</v>
+        <v>4.925771951675415</v>
       </c>
       <c r="J8" t="n">
-        <v>4.232189893722534</v>
+        <v>4.625663280487061</v>
       </c>
       <c r="K8" t="n">
-        <v>3.934689998626709</v>
+        <v>4.114532709121704</v>
       </c>
       <c r="L8" t="n">
-        <v>4.10876088142395</v>
+        <v>4.363097620010376</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>4.235099792480469</v>
+        <v>3.857072114944458</v>
       </c>
       <c r="C9" t="n">
-        <v>4.203569889068604</v>
+        <v>3.887395143508911</v>
       </c>
       <c r="D9" t="n">
-        <v>3.872354745864868</v>
+        <v>4.16097092628479</v>
       </c>
       <c r="E9" t="n">
-        <v>3.763684511184692</v>
+        <v>4.432723522186279</v>
       </c>
       <c r="F9" t="n">
-        <v>3.765471696853638</v>
+        <v>3.888127326965332</v>
       </c>
       <c r="G9" t="n">
-        <v>3.968193769454956</v>
+        <v>4.012546062469482</v>
       </c>
       <c r="H9" t="n">
-        <v>4.612819194793701</v>
+        <v>3.98817777633667</v>
       </c>
       <c r="I9" t="n">
-        <v>4.555111169815063</v>
+        <v>4.490111589431763</v>
       </c>
       <c r="J9" t="n">
-        <v>4.177752017974854</v>
+        <v>4.290180206298828</v>
       </c>
       <c r="K9" t="n">
-        <v>5.286388874053955</v>
+        <v>4.213683128356934</v>
       </c>
       <c r="L9" t="n">
-        <v>4.24404456615448</v>
+        <v>4.122098779678344</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.454581499099731</v>
+        <v>5.343129634857178</v>
       </c>
       <c r="C10" t="n">
-        <v>5.147436380386353</v>
+        <v>6.086879014968872</v>
       </c>
       <c r="D10" t="n">
-        <v>5.426883220672607</v>
+        <v>5.118540287017822</v>
       </c>
       <c r="E10" t="n">
-        <v>5.429901361465454</v>
+        <v>5.169438362121582</v>
       </c>
       <c r="F10" t="n">
-        <v>5.611893177032471</v>
+        <v>5.454182863235474</v>
       </c>
       <c r="G10" t="n">
-        <v>5.480928182601929</v>
+        <v>5.208500385284424</v>
       </c>
       <c r="H10" t="n">
-        <v>5.089809417724609</v>
+        <v>5.085270166397095</v>
       </c>
       <c r="I10" t="n">
-        <v>5.755891561508179</v>
+        <v>5.136143684387207</v>
       </c>
       <c r="J10" t="n">
-        <v>5.574589252471924</v>
+        <v>6.081799268722534</v>
       </c>
       <c r="K10" t="n">
-        <v>6.329880237579346</v>
+        <v>5.473871946334839</v>
       </c>
       <c r="L10" t="n">
-        <v>5.53017942905426</v>
+        <v>5.415775561332703</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.29630708694458</v>
+        <v>4.375432252883911</v>
       </c>
       <c r="C11" t="n">
-        <v>4.544686079025269</v>
+        <v>5.392033576965332</v>
       </c>
       <c r="D11" t="n">
-        <v>4.771562337875366</v>
+        <v>4.954421997070312</v>
       </c>
       <c r="E11" t="n">
-        <v>4.889774799346924</v>
+        <v>4.812174797058105</v>
       </c>
       <c r="F11" t="n">
-        <v>4.277848720550537</v>
+        <v>4.989425182342529</v>
       </c>
       <c r="G11" t="n">
-        <v>4.76758861541748</v>
+        <v>5.131214618682861</v>
       </c>
       <c r="H11" t="n">
-        <v>4.519747257232666</v>
+        <v>4.456825733184814</v>
       </c>
       <c r="I11" t="n">
-        <v>4.612972497940063</v>
+        <v>4.743715763092041</v>
       </c>
       <c r="J11" t="n">
-        <v>4.332223415374756</v>
+        <v>4.860212087631226</v>
       </c>
       <c r="K11" t="n">
-        <v>4.503768682479858</v>
+        <v>4.874045610427856</v>
       </c>
       <c r="L11" t="n">
-        <v>4.55164794921875</v>
+        <v>4.858950161933899</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.823574781417847</v>
+        <v>4.307379961013794</v>
       </c>
       <c r="C12" t="n">
-        <v>3.924342632293701</v>
+        <v>4.127592325210571</v>
       </c>
       <c r="D12" t="n">
-        <v>4.107829332351685</v>
+        <v>4.202647924423218</v>
       </c>
       <c r="E12" t="n">
-        <v>4.097821712493896</v>
+        <v>3.862258434295654</v>
       </c>
       <c r="F12" t="n">
-        <v>3.832038402557373</v>
+        <v>4.065859317779541</v>
       </c>
       <c r="G12" t="n">
-        <v>4.124756336212158</v>
+        <v>4.252145051956177</v>
       </c>
       <c r="H12" t="n">
-        <v>3.92626690864563</v>
+        <v>4.163562536239624</v>
       </c>
       <c r="I12" t="n">
-        <v>3.903323888778687</v>
+        <v>4.246361017227173</v>
       </c>
       <c r="J12" t="n">
-        <v>4.163145065307617</v>
+        <v>4.201630353927612</v>
       </c>
       <c r="K12" t="n">
-        <v>4.200544357299805</v>
+        <v>4.00680136680603</v>
       </c>
       <c r="L12" t="n">
-        <v>4.01036434173584</v>
+        <v>4.143623828887939</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.503273963928223</v>
+        <v>4.196791172027588</v>
       </c>
       <c r="C13" t="n">
-        <v>3.992597103118896</v>
+        <v>4.124673843383789</v>
       </c>
       <c r="D13" t="n">
-        <v>3.998578071594238</v>
+        <v>4.425222873687744</v>
       </c>
       <c r="E13" t="n">
-        <v>3.950716733932495</v>
+        <v>4.404027462005615</v>
       </c>
       <c r="F13" t="n">
-        <v>3.94321084022522</v>
+        <v>4.236953020095825</v>
       </c>
       <c r="G13" t="n">
-        <v>3.883387327194214</v>
+        <v>4.17172908782959</v>
       </c>
       <c r="H13" t="n">
-        <v>3.815098524093628</v>
+        <v>4.086501359939575</v>
       </c>
       <c r="I13" t="n">
-        <v>3.801488637924194</v>
+        <v>4.511385202407837</v>
       </c>
       <c r="J13" t="n">
-        <v>4.024758338928223</v>
+        <v>4.409180402755737</v>
       </c>
       <c r="K13" t="n">
-        <v>3.824239730834961</v>
+        <v>4.451075077056885</v>
       </c>
       <c r="L13" t="n">
-        <v>3.973734927177429</v>
+        <v>4.301753950119019</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>4.266622066497803</v>
+        <v>4.633030414581299</v>
       </c>
       <c r="C14" t="n">
-        <v>4.313507318496704</v>
+        <v>4.526002407073975</v>
       </c>
       <c r="D14" t="n">
-        <v>4.278057813644409</v>
+        <v>4.428672075271606</v>
       </c>
       <c r="E14" t="n">
-        <v>4.694529056549072</v>
+        <v>4.31640100479126</v>
       </c>
       <c r="F14" t="n">
-        <v>4.194320678710938</v>
+        <v>4.395553588867188</v>
       </c>
       <c r="G14" t="n">
-        <v>4.470127105712891</v>
+        <v>4.414113759994507</v>
       </c>
       <c r="H14" t="n">
-        <v>4.027730464935303</v>
+        <v>4.716894865036011</v>
       </c>
       <c r="I14" t="n">
-        <v>4.815714359283447</v>
+        <v>4.273755550384521</v>
       </c>
       <c r="J14" t="n">
-        <v>4.220241785049438</v>
+        <v>4.833472490310669</v>
       </c>
       <c r="K14" t="n">
-        <v>4.291558027267456</v>
+        <v>4.439371585845947</v>
       </c>
       <c r="L14" t="n">
-        <v>4.357240867614746</v>
+        <v>4.497726774215698</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.373860359191895</v>
+        <v>4.460484027862549</v>
       </c>
       <c r="C15" t="n">
-        <v>4.248155355453491</v>
+        <v>4.813957452774048</v>
       </c>
       <c r="D15" t="n">
-        <v>4.499030828475952</v>
+        <v>4.660670042037964</v>
       </c>
       <c r="E15" t="n">
-        <v>4.56284499168396</v>
+        <v>4.908862829208374</v>
       </c>
       <c r="F15" t="n">
-        <v>4.438208341598511</v>
+        <v>4.821128129959106</v>
       </c>
       <c r="G15" t="n">
-        <v>4.381328582763672</v>
+        <v>4.476712465286255</v>
       </c>
       <c r="H15" t="n">
-        <v>4.630716562271118</v>
+        <v>4.642158985137939</v>
       </c>
       <c r="I15" t="n">
-        <v>4.380456209182739</v>
+        <v>4.927162647247314</v>
       </c>
       <c r="J15" t="n">
-        <v>4.670374870300293</v>
+        <v>4.809904813766479</v>
       </c>
       <c r="K15" t="n">
-        <v>4.610004901885986</v>
+        <v>4.790399312973022</v>
       </c>
       <c r="L15" t="n">
-        <v>4.479498100280762</v>
+        <v>4.731144070625305</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>3.863449573516846</v>
+        <v>4.447910785675049</v>
       </c>
       <c r="C16" t="n">
-        <v>4.158669948577881</v>
+        <v>4.313442707061768</v>
       </c>
       <c r="D16" t="n">
-        <v>4.553148031234741</v>
+        <v>4.310692548751831</v>
       </c>
       <c r="E16" t="n">
-        <v>4.494284152984619</v>
+        <v>4.339776277542114</v>
       </c>
       <c r="F16" t="n">
-        <v>4.719247102737427</v>
+        <v>4.372962713241577</v>
       </c>
       <c r="G16" t="n">
-        <v>4.478842496871948</v>
+        <v>5.012462377548218</v>
       </c>
       <c r="H16" t="n">
-        <v>4.493811845779419</v>
+        <v>4.91634464263916</v>
       </c>
       <c r="I16" t="n">
-        <v>4.368627071380615</v>
+        <v>4.650179862976074</v>
       </c>
       <c r="J16" t="n">
-        <v>4.468365907669067</v>
+        <v>4.661402225494385</v>
       </c>
       <c r="K16" t="n">
-        <v>4.598012685775757</v>
+        <v>4.834802150726318</v>
       </c>
       <c r="L16" t="n">
-        <v>4.419645881652832</v>
+        <v>4.585997629165649</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.342680692672729</v>
+        <v>5.489802360534668</v>
       </c>
       <c r="C17" t="n">
-        <v>4.407509326934814</v>
+        <v>4.815804481506348</v>
       </c>
       <c r="D17" t="n">
-        <v>5.065813302993774</v>
+        <v>4.945780754089355</v>
       </c>
       <c r="E17" t="n">
-        <v>4.536333084106445</v>
+        <v>4.373823404312134</v>
       </c>
       <c r="F17" t="n">
-        <v>4.939402103424072</v>
+        <v>4.899621963500977</v>
       </c>
       <c r="G17" t="n">
-        <v>4.991785049438477</v>
+        <v>5.17050313949585</v>
       </c>
       <c r="H17" t="n">
-        <v>4.950368642807007</v>
+        <v>4.7298424243927</v>
       </c>
       <c r="I17" t="n">
-        <v>4.807737827301025</v>
+        <v>4.579868078231812</v>
       </c>
       <c r="J17" t="n">
-        <v>4.589293003082275</v>
+        <v>4.866399765014648</v>
       </c>
       <c r="K17" t="n">
-        <v>4.898149967193604</v>
+        <v>4.862074613571167</v>
       </c>
       <c r="L17" t="n">
-        <v>4.752907299995423</v>
+        <v>4.873352098464966</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.104053258895874</v>
+        <v>4.38909912109375</v>
       </c>
       <c r="C18" t="n">
-        <v>3.718113660812378</v>
+        <v>4.084708452224731</v>
       </c>
       <c r="D18" t="n">
-        <v>4.034707307815552</v>
+        <v>4.343837976455688</v>
       </c>
       <c r="E18" t="n">
-        <v>3.948424577713013</v>
+        <v>4.104413032531738</v>
       </c>
       <c r="F18" t="n">
-        <v>4.084110260009766</v>
+        <v>4.191365480422974</v>
       </c>
       <c r="G18" t="n">
-        <v>4.018784761428833</v>
+        <v>3.90532922744751</v>
       </c>
       <c r="H18" t="n">
-        <v>3.795339822769165</v>
+        <v>4.69806957244873</v>
       </c>
       <c r="I18" t="n">
-        <v>4.141928911209106</v>
+        <v>3.800339460372925</v>
       </c>
       <c r="J18" t="n">
-        <v>3.778352975845337</v>
+        <v>3.910537958145142</v>
       </c>
       <c r="K18" t="n">
-        <v>3.999784231185913</v>
+        <v>4.294718980789185</v>
       </c>
       <c r="L18" t="n">
-        <v>3.962359976768494</v>
+        <v>4.172241926193237</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.872573852539062</v>
+        <v>5.057876348495483</v>
       </c>
       <c r="C19" t="n">
-        <v>4.438201427459717</v>
+        <v>4.747832298278809</v>
       </c>
       <c r="D19" t="n">
-        <v>4.650138854980469</v>
+        <v>5.257010698318481</v>
       </c>
       <c r="E19" t="n">
-        <v>4.651130199432373</v>
+        <v>5.277247190475464</v>
       </c>
       <c r="F19" t="n">
-        <v>4.611250162124634</v>
+        <v>5.199942111968994</v>
       </c>
       <c r="G19" t="n">
-        <v>4.450167417526245</v>
+        <v>5.087512254714966</v>
       </c>
       <c r="H19" t="n">
-        <v>4.452656507492065</v>
+        <v>4.768131494522095</v>
       </c>
       <c r="I19" t="n">
-        <v>4.173348903656006</v>
+        <v>4.754135131835938</v>
       </c>
       <c r="J19" t="n">
-        <v>4.510027885437012</v>
+        <v>4.666893005371094</v>
       </c>
       <c r="K19" t="n">
-        <v>4.576358556747437</v>
+        <v>4.945584297180176</v>
       </c>
       <c r="L19" t="n">
-        <v>4.538585376739502</v>
+        <v>4.97621648311615</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.386810302734375</v>
+        <v>4.540496110916138</v>
       </c>
       <c r="C20" t="n">
-        <v>4.709506750106812</v>
+        <v>4.327644109725952</v>
       </c>
       <c r="D20" t="n">
-        <v>4.492108821868896</v>
+        <v>4.378776788711548</v>
       </c>
       <c r="E20" t="n">
-        <v>4.18111515045166</v>
+        <v>4.4128737449646</v>
       </c>
       <c r="F20" t="n">
-        <v>4.177672624588013</v>
+        <v>5.496694087982178</v>
       </c>
       <c r="G20" t="n">
-        <v>4.093840837478638</v>
+        <v>4.640649795532227</v>
       </c>
       <c r="H20" t="n">
-        <v>4.239454746246338</v>
+        <v>4.643046140670776</v>
       </c>
       <c r="I20" t="n">
-        <v>4.285850286483765</v>
+        <v>4.263603448867798</v>
       </c>
       <c r="J20" t="n">
-        <v>4.183108806610107</v>
+        <v>4.271666526794434</v>
       </c>
       <c r="K20" t="n">
-        <v>4.438455820083618</v>
+        <v>4.349097490310669</v>
       </c>
       <c r="L20" t="n">
-        <v>4.418792414665222</v>
+        <v>4.532454824447631</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.403016567230225</v>
+        <v>4.471655607223511</v>
       </c>
       <c r="C21" t="n">
-        <v>4.400560140609741</v>
+        <v>4.897857189178467</v>
       </c>
       <c r="D21" t="n">
-        <v>4.572112798690796</v>
+        <v>4.799500226974487</v>
       </c>
       <c r="E21" t="n">
-        <v>4.348176240921021</v>
+        <v>4.877363920211792</v>
       </c>
       <c r="F21" t="n">
-        <v>4.330797433853149</v>
+        <v>4.674813508987427</v>
       </c>
       <c r="G21" t="n">
-        <v>4.351170301437378</v>
+        <v>4.67899489402771</v>
       </c>
       <c r="H21" t="n">
-        <v>4.87082839012146</v>
+        <v>4.609963417053223</v>
       </c>
       <c r="I21" t="n">
-        <v>4.62995719909668</v>
+        <v>5.039362907409668</v>
       </c>
       <c r="J21" t="n">
-        <v>4.641896963119507</v>
+        <v>4.651177167892456</v>
       </c>
       <c r="K21" t="n">
-        <v>4.606992244720459</v>
+        <v>4.535732746124268</v>
       </c>
       <c r="L21" t="n">
-        <v>4.515550827980041</v>
+        <v>4.723642158508301</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.451396226882935</v>
+        <v>4.95624828338623</v>
       </c>
       <c r="C22" t="n">
-        <v>4.421975612640381</v>
+        <v>4.754679918289185</v>
       </c>
       <c r="D22" t="n">
-        <v>4.774083137512207</v>
+        <v>4.459997415542603</v>
       </c>
       <c r="E22" t="n">
-        <v>4.551147222518921</v>
+        <v>4.681416034698486</v>
       </c>
       <c r="F22" t="n">
-        <v>4.501770257949829</v>
+        <v>5.456210613250732</v>
       </c>
       <c r="G22" t="n">
-        <v>4.459376335144043</v>
+        <v>4.576536893844604</v>
       </c>
       <c r="H22" t="n">
-        <v>4.521781444549561</v>
+        <v>4.941469669342041</v>
       </c>
       <c r="I22" t="n">
-        <v>4.041470766067505</v>
+        <v>4.828528165817261</v>
       </c>
       <c r="J22" t="n">
-        <v>4.33970046043396</v>
+        <v>4.760033845901489</v>
       </c>
       <c r="K22" t="n">
-        <v>4.604010105133057</v>
+        <v>4.959059000015259</v>
       </c>
       <c r="L22" t="n">
-        <v>4.46667115688324</v>
+        <v>4.837417984008789</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.793509960174561</v>
+        <v>5.061617136001587</v>
       </c>
       <c r="C23" t="n">
-        <v>4.546684265136719</v>
+        <v>4.733777523040771</v>
       </c>
       <c r="D23" t="n">
-        <v>4.955110549926758</v>
+        <v>4.731178522109985</v>
       </c>
       <c r="E23" t="n">
-        <v>4.610992908477783</v>
+        <v>5.167065620422363</v>
       </c>
       <c r="F23" t="n">
-        <v>4.708237171173096</v>
+        <v>4.981708288192749</v>
       </c>
       <c r="G23" t="n">
-        <v>5.554149389266968</v>
+        <v>5.192315101623535</v>
       </c>
       <c r="H23" t="n">
-        <v>5.444943904876709</v>
+        <v>5.046652317047119</v>
       </c>
       <c r="I23" t="n">
-        <v>5.656880617141724</v>
+        <v>4.784394502639771</v>
       </c>
       <c r="J23" t="n">
-        <v>5.100273609161377</v>
+        <v>5.02373480796814</v>
       </c>
       <c r="K23" t="n">
-        <v>4.73017144203186</v>
+        <v>4.626382112503052</v>
       </c>
       <c r="L23" t="n">
-        <v>5.010095381736756</v>
+        <v>4.934882593154907</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>3.907326936721802</v>
+        <v>4.197733402252197</v>
       </c>
       <c r="C24" t="n">
-        <v>4.152706146240234</v>
+        <v>4.530848979949951</v>
       </c>
       <c r="D24" t="n">
-        <v>4.309296846389771</v>
+        <v>4.812475442886353</v>
       </c>
       <c r="E24" t="n">
-        <v>4.115774631500244</v>
+        <v>4.764853000640869</v>
       </c>
       <c r="F24" t="n">
-        <v>4.468875885009766</v>
+        <v>4.202598333358765</v>
       </c>
       <c r="G24" t="n">
-        <v>4.448417663574219</v>
+        <v>4.486840724945068</v>
       </c>
       <c r="H24" t="n">
-        <v>3.920310735702515</v>
+        <v>4.666785001754761</v>
       </c>
       <c r="I24" t="n">
-        <v>4.247439861297607</v>
+        <v>4.53322172164917</v>
       </c>
       <c r="J24" t="n">
-        <v>4.533687829971313</v>
+        <v>4.800129413604736</v>
       </c>
       <c r="K24" t="n">
-        <v>4.062425136566162</v>
+        <v>4.567169904708862</v>
       </c>
       <c r="L24" t="n">
-        <v>4.216626167297363</v>
+        <v>4.556265592575073</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.822043418884277</v>
+        <v>3.900978565216064</v>
       </c>
       <c r="C25" t="n">
-        <v>3.809089183807373</v>
+        <v>4.222781419754028</v>
       </c>
       <c r="D25" t="n">
-        <v>4.128774166107178</v>
+        <v>3.968039512634277</v>
       </c>
       <c r="E25" t="n">
-        <v>4.117769002914429</v>
+        <v>4.61467432975769</v>
       </c>
       <c r="F25" t="n">
-        <v>3.683904886245728</v>
+        <v>4.101978540420532</v>
       </c>
       <c r="G25" t="n">
-        <v>4.114768266677856</v>
+        <v>4.366318464279175</v>
       </c>
       <c r="H25" t="n">
-        <v>4.147689819335938</v>
+        <v>3.950220346450806</v>
       </c>
       <c r="I25" t="n">
-        <v>3.924268484115601</v>
+        <v>4.210028886795044</v>
       </c>
       <c r="J25" t="n">
-        <v>3.82413649559021</v>
+        <v>3.794143199920654</v>
       </c>
       <c r="K25" t="n">
-        <v>3.871425867080688</v>
+        <v>4.454649686813354</v>
       </c>
       <c r="L25" t="n">
-        <v>3.944386959075928</v>
+        <v>4.158381295204163</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.746651649475098</v>
+        <v>4.906112670898438</v>
       </c>
       <c r="C26" t="n">
-        <v>4.723557472229004</v>
+        <v>4.970503330230713</v>
       </c>
       <c r="D26" t="n">
-        <v>4.448656320571899</v>
+        <v>4.658650398254395</v>
       </c>
       <c r="E26" t="n">
-        <v>4.589350700378418</v>
+        <v>4.720177412033081</v>
       </c>
       <c r="F26" t="n">
-        <v>4.549880743026733</v>
+        <v>4.673622846603394</v>
       </c>
       <c r="G26" t="n">
-        <v>4.398802995681763</v>
+        <v>4.950997114181519</v>
       </c>
       <c r="H26" t="n">
-        <v>4.53696346282959</v>
+        <v>4.784160852432251</v>
       </c>
       <c r="I26" t="n">
-        <v>4.531465530395508</v>
+        <v>4.670515775680542</v>
       </c>
       <c r="J26" t="n">
-        <v>4.38429594039917</v>
+        <v>4.87803053855896</v>
       </c>
       <c r="K26" t="n">
-        <v>4.712485074996948</v>
+        <v>4.57877516746521</v>
       </c>
       <c r="L26" t="n">
-        <v>4.562210988998413</v>
+        <v>4.77915461063385</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>5.170808553695679</v>
+        <v>5.396351337432861</v>
       </c>
       <c r="C27" t="n">
-        <v>5.326917409896851</v>
+        <v>5.258522510528564</v>
       </c>
       <c r="D27" t="n">
-        <v>5.079551458358765</v>
+        <v>5.19529914855957</v>
       </c>
       <c r="E27" t="n">
-        <v>4.65314793586731</v>
+        <v>5.51667308807373</v>
       </c>
       <c r="F27" t="n">
-        <v>5.734864711761475</v>
+        <v>5.330147981643677</v>
       </c>
       <c r="G27" t="n">
-        <v>4.531437397003174</v>
+        <v>5.050101757049561</v>
       </c>
       <c r="H27" t="n">
-        <v>4.595275402069092</v>
+        <v>5.194377422332764</v>
       </c>
       <c r="I27" t="n">
-        <v>4.924937963485718</v>
+        <v>5.184911727905273</v>
       </c>
       <c r="J27" t="n">
-        <v>4.645153522491455</v>
+        <v>5.04044508934021</v>
       </c>
       <c r="K27" t="n">
-        <v>4.701529979705811</v>
+        <v>4.937310695648193</v>
       </c>
       <c r="L27" t="n">
-        <v>4.936362433433533</v>
+        <v>5.210414075851441</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.37883734703064</v>
+        <v>4.619938373565674</v>
       </c>
       <c r="C28" t="n">
-        <v>4.179851293563843</v>
+        <v>4.45254921913147</v>
       </c>
       <c r="D28" t="n">
-        <v>4.177347898483276</v>
+        <v>4.6166672706604</v>
       </c>
       <c r="E28" t="n">
-        <v>4.081092596054077</v>
+        <v>4.654814004898071</v>
       </c>
       <c r="F28" t="n">
-        <v>4.209259510040283</v>
+        <v>4.207089424133301</v>
       </c>
       <c r="G28" t="n">
-        <v>4.080098152160645</v>
+        <v>4.384079933166504</v>
       </c>
       <c r="H28" t="n">
-        <v>4.078584432601929</v>
+        <v>4.448235750198364</v>
       </c>
       <c r="I28" t="n">
-        <v>4.519992113113403</v>
+        <v>4.586639642715454</v>
       </c>
       <c r="J28" t="n">
-        <v>4.130972146987915</v>
+        <v>4.382402658462524</v>
       </c>
       <c r="K28" t="n">
-        <v>4.132455348968506</v>
+        <v>4.77429986000061</v>
       </c>
       <c r="L28" t="n">
-        <v>4.196849083900451</v>
+        <v>4.512671613693238</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.306556940078735</v>
+        <v>5.168888092041016</v>
       </c>
       <c r="C29" t="n">
-        <v>4.330468893051147</v>
+        <v>4.44672417640686</v>
       </c>
       <c r="D29" t="n">
-        <v>5.504462003707886</v>
+        <v>4.390433311462402</v>
       </c>
       <c r="E29" t="n">
-        <v>4.444170713424683</v>
+        <v>4.480973482131958</v>
       </c>
       <c r="F29" t="n">
-        <v>4.837652921676636</v>
+        <v>5.367843151092529</v>
       </c>
       <c r="G29" t="n">
-        <v>5.095505952835083</v>
+        <v>4.874708652496338</v>
       </c>
       <c r="H29" t="n">
-        <v>5.014215230941772</v>
+        <v>4.349457979202271</v>
       </c>
       <c r="I29" t="n">
-        <v>4.157872915267944</v>
+        <v>5.00299596786499</v>
       </c>
       <c r="J29" t="n">
-        <v>4.491071462631226</v>
+        <v>5.238904237747192</v>
       </c>
       <c r="K29" t="n">
-        <v>4.642139911651611</v>
+        <v>4.886435031890869</v>
       </c>
       <c r="L29" t="n">
-        <v>4.682411694526673</v>
+        <v>4.820736408233643</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.177359104156494</v>
+        <v>4.387856483459473</v>
       </c>
       <c r="C30" t="n">
-        <v>4.198281764984131</v>
+        <v>4.339450120925903</v>
       </c>
       <c r="D30" t="n">
-        <v>4.46759557723999</v>
+        <v>4.146634817123413</v>
       </c>
       <c r="E30" t="n">
-        <v>4.282577991485596</v>
+        <v>4.332921743392944</v>
       </c>
       <c r="F30" t="n">
-        <v>4.041672706604004</v>
+        <v>4.210771799087524</v>
       </c>
       <c r="G30" t="n">
-        <v>4.180345058441162</v>
+        <v>4.240760326385498</v>
       </c>
       <c r="H30" t="n">
-        <v>4.23422384262085</v>
+        <v>4.571373462677002</v>
       </c>
       <c r="I30" t="n">
-        <v>4.003123998641968</v>
+        <v>4.863019227981567</v>
       </c>
       <c r="J30" t="n">
-        <v>4.148704051971436</v>
+        <v>4.536309480667114</v>
       </c>
       <c r="K30" t="n">
-        <v>4.022016286849976</v>
+        <v>4.302756786346436</v>
       </c>
       <c r="L30" t="n">
-        <v>4.175590038299561</v>
+        <v>4.393185424804687</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>4.172885894775391</v>
+        <v>4.184653043746948</v>
       </c>
       <c r="C31" t="n">
-        <v>3.938951015472412</v>
+        <v>4.339427947998047</v>
       </c>
       <c r="D31" t="n">
-        <v>4.132977724075317</v>
+        <v>4.221149444580078</v>
       </c>
       <c r="E31" t="n">
-        <v>4.229198694229126</v>
+        <v>4.200347423553467</v>
       </c>
       <c r="F31" t="n">
-        <v>4.023748159408569</v>
+        <v>4.662969589233398</v>
       </c>
       <c r="G31" t="n">
-        <v>4.018742799758911</v>
+        <v>4.66570782661438</v>
       </c>
       <c r="H31" t="n">
-        <v>4.075101852416992</v>
+        <v>4.236236810684204</v>
       </c>
       <c r="I31" t="n">
-        <v>4.157896995544434</v>
+        <v>3.911916971206665</v>
       </c>
       <c r="J31" t="n">
-        <v>4.105028390884399</v>
+        <v>4.226523876190186</v>
       </c>
       <c r="K31" t="n">
-        <v>3.951983213424683</v>
+        <v>4.240220546722412</v>
       </c>
       <c r="L31" t="n">
-        <v>4.080651473999024</v>
+        <v>4.288915348052979</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.300542593002319</v>
+        <v>4.370485067367554</v>
       </c>
       <c r="C32" t="n">
-        <v>4.271114587783813</v>
+        <v>4.008428335189819</v>
       </c>
       <c r="D32" t="n">
-        <v>3.898592233657837</v>
+        <v>4.16990327835083</v>
       </c>
       <c r="E32" t="n">
-        <v>4.507998704910278</v>
+        <v>4.577808380126953</v>
       </c>
       <c r="F32" t="n">
-        <v>4.096037864685059</v>
+        <v>5.030839204788208</v>
       </c>
       <c r="G32" t="n">
-        <v>4.141943693161011</v>
+        <v>4.430091619491577</v>
       </c>
       <c r="H32" t="n">
-        <v>4.139441251754761</v>
+        <v>4.376736640930176</v>
       </c>
       <c r="I32" t="n">
-        <v>4.157891035079956</v>
+        <v>3.999212265014648</v>
       </c>
       <c r="J32" t="n">
-        <v>4.001787424087524</v>
+        <v>4.096006631851196</v>
       </c>
       <c r="K32" t="n">
-        <v>4.248106956481934</v>
+        <v>4.537223815917969</v>
       </c>
       <c r="L32" t="n">
-        <v>4.176345634460449</v>
+        <v>4.359673523902893</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>5.181796312332153</v>
+        <v>4.253006935119629</v>
       </c>
       <c r="C33" t="n">
-        <v>4.507988691329956</v>
+        <v>4.81148886680603</v>
       </c>
       <c r="D33" t="n">
-        <v>4.317477703094482</v>
+        <v>4.646101236343384</v>
       </c>
       <c r="E33" t="n">
-        <v>4.366874694824219</v>
+        <v>4.853368759155273</v>
       </c>
       <c r="F33" t="n">
-        <v>4.388327121734619</v>
+        <v>4.432866811752319</v>
       </c>
       <c r="G33" t="n">
-        <v>4.526468276977539</v>
+        <v>4.614177465438843</v>
       </c>
       <c r="H33" t="n">
-        <v>4.449630975723267</v>
+        <v>4.685882806777954</v>
       </c>
       <c r="I33" t="n">
-        <v>4.250148057937622</v>
+        <v>5.195197582244873</v>
       </c>
       <c r="J33" t="n">
-        <v>4.245665311813354</v>
+        <v>4.438650846481323</v>
       </c>
       <c r="K33" t="n">
-        <v>4.401764154434204</v>
+        <v>4.59738564491272</v>
       </c>
       <c r="L33" t="n">
-        <v>4.463614130020142</v>
+        <v>4.652812695503235</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.716015577316284</v>
+        <v>4.194940090179443</v>
       </c>
       <c r="C34" t="n">
-        <v>3.690080404281616</v>
+        <v>4.032094478607178</v>
       </c>
       <c r="D34" t="n">
-        <v>3.781840324401855</v>
+        <v>4.272239923477173</v>
       </c>
       <c r="E34" t="n">
-        <v>3.988826274871826</v>
+        <v>3.828750610351562</v>
       </c>
       <c r="F34" t="n">
-        <v>3.785341024398804</v>
+        <v>4.107586145401001</v>
       </c>
       <c r="G34" t="n">
-        <v>3.941432476043701</v>
+        <v>4.136698246002197</v>
       </c>
       <c r="H34" t="n">
-        <v>4.001792192459106</v>
+        <v>3.971558570861816</v>
       </c>
       <c r="I34" t="n">
-        <v>3.840213298797607</v>
+        <v>4.127105712890625</v>
       </c>
       <c r="J34" t="n">
-        <v>3.824781656265259</v>
+        <v>3.9221510887146</v>
       </c>
       <c r="K34" t="n">
-        <v>3.993343114852905</v>
+        <v>3.965952157974243</v>
       </c>
       <c r="L34" t="n">
-        <v>3.856366634368896</v>
+        <v>4.055907702445984</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.665088415145874</v>
+        <v>4.889216423034668</v>
       </c>
       <c r="C35" t="n">
-        <v>5.626701593399048</v>
+        <v>5.168684482574463</v>
       </c>
       <c r="D35" t="n">
-        <v>5.405227899551392</v>
+        <v>5.018459320068359</v>
       </c>
       <c r="E35" t="n">
-        <v>4.718485116958618</v>
+        <v>5.629568576812744</v>
       </c>
       <c r="F35" t="n">
-        <v>5.036180019378662</v>
+        <v>5.224231004714966</v>
       </c>
       <c r="G35" t="n">
-        <v>4.690561532974243</v>
+        <v>5.005364179611206</v>
       </c>
       <c r="H35" t="n">
-        <v>4.830672740936279</v>
+        <v>5.354628562927246</v>
       </c>
       <c r="I35" t="n">
-        <v>4.918972253799438</v>
+        <v>4.755626201629639</v>
       </c>
       <c r="J35" t="n">
-        <v>4.760859727859497</v>
+        <v>5.111312627792358</v>
       </c>
       <c r="K35" t="n">
-        <v>5.060085296630859</v>
+        <v>5.166944742202759</v>
       </c>
       <c r="L35" t="n">
-        <v>4.971283459663391</v>
+        <v>5.132403612136841</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.646710634231567</v>
+        <v>3.706831693649292</v>
       </c>
       <c r="C36" t="n">
-        <v>3.536470413208008</v>
+        <v>3.979910850524902</v>
       </c>
       <c r="D36" t="n">
-        <v>4.120039463043213</v>
+        <v>3.847678422927856</v>
       </c>
       <c r="E36" t="n">
-        <v>3.640213489532471</v>
+        <v>4.005351543426514</v>
       </c>
       <c r="F36" t="n">
-        <v>3.569703340530396</v>
+        <v>3.801473379135132</v>
       </c>
       <c r="G36" t="n">
-        <v>3.776166677474976</v>
+        <v>3.844776391983032</v>
       </c>
       <c r="H36" t="n">
-        <v>3.643524646759033</v>
+        <v>3.788941621780396</v>
       </c>
       <c r="I36" t="n">
-        <v>3.610602140426636</v>
+        <v>3.786869287490845</v>
       </c>
       <c r="J36" t="n">
-        <v>3.547762155532837</v>
+        <v>3.883257627487183</v>
       </c>
       <c r="K36" t="n">
-        <v>3.698902130126953</v>
+        <v>3.702145576477051</v>
       </c>
       <c r="L36" t="n">
-        <v>3.679009509086609</v>
+        <v>3.83472363948822</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.206045627593994</v>
+        <v>4.7512047290802</v>
       </c>
       <c r="C37" t="n">
-        <v>4.34718656539917</v>
+        <v>4.627431154251099</v>
       </c>
       <c r="D37" t="n">
-        <v>4.68729043006897</v>
+        <v>5.173998832702637</v>
       </c>
       <c r="E37" t="n">
-        <v>4.483824491500854</v>
+        <v>4.946279764175415</v>
       </c>
       <c r="F37" t="n">
-        <v>4.388079166412354</v>
+        <v>4.919227838516235</v>
       </c>
       <c r="G37" t="n">
-        <v>4.537184953689575</v>
+        <v>4.595042943954468</v>
       </c>
       <c r="H37" t="n">
-        <v>4.555650472640991</v>
+        <v>4.717101812362671</v>
       </c>
       <c r="I37" t="n">
-        <v>4.475847005844116</v>
+        <v>4.493141174316406</v>
       </c>
       <c r="J37" t="n">
-        <v>4.440427541732788</v>
+        <v>4.714010238647461</v>
       </c>
       <c r="K37" t="n">
-        <v>4.459890842437744</v>
+        <v>4.809183120727539</v>
       </c>
       <c r="L37" t="n">
-        <v>4.458142709732056</v>
+        <v>4.774662160873413</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.451406002044678</v>
+        <v>4.840967178344727</v>
       </c>
       <c r="C38" t="n">
-        <v>5.206435441970825</v>
+        <v>4.761118412017822</v>
       </c>
       <c r="D38" t="n">
-        <v>5.219417810440063</v>
+        <v>4.545562505722046</v>
       </c>
       <c r="E38" t="n">
-        <v>5.532139539718628</v>
+        <v>4.948736429214478</v>
       </c>
       <c r="F38" t="n">
-        <v>4.713229417800903</v>
+        <v>4.56959080696106</v>
       </c>
       <c r="G38" t="n">
-        <v>4.574084520339966</v>
+        <v>5.170353174209595</v>
       </c>
       <c r="H38" t="n">
-        <v>4.446401834487915</v>
+        <v>5.239318132400513</v>
       </c>
       <c r="I38" t="n">
-        <v>4.376601934432983</v>
+        <v>4.741026163101196</v>
       </c>
       <c r="J38" t="n">
-        <v>4.899094343185425</v>
+        <v>4.605754137039185</v>
       </c>
       <c r="K38" t="n">
-        <v>5.385799407958984</v>
+        <v>4.895879745483398</v>
       </c>
       <c r="L38" t="n">
-        <v>4.880461025238037</v>
+        <v>4.831830668449402</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.066616296768188</v>
+        <v>4.064665555953979</v>
       </c>
       <c r="C39" t="n">
-        <v>3.679131984710693</v>
+        <v>3.908868074417114</v>
       </c>
       <c r="D39" t="n">
-        <v>4.418734073638916</v>
+        <v>4.119347333908081</v>
       </c>
       <c r="E39" t="n">
-        <v>3.997801065444946</v>
+        <v>4.479315042495728</v>
       </c>
       <c r="F39" t="n">
-        <v>3.773859262466431</v>
+        <v>5.378546714782715</v>
       </c>
       <c r="G39" t="n">
-        <v>3.818798303604126</v>
+        <v>3.926962852478027</v>
       </c>
       <c r="H39" t="n">
-        <v>3.801795244216919</v>
+        <v>4.109577655792236</v>
       </c>
       <c r="I39" t="n">
-        <v>3.766392707824707</v>
+        <v>4.935321807861328</v>
       </c>
       <c r="J39" t="n">
-        <v>3.960919618606567</v>
+        <v>4.163061618804932</v>
       </c>
       <c r="K39" t="n">
-        <v>3.985347509384155</v>
+        <v>4.278522253036499</v>
       </c>
       <c r="L39" t="n">
-        <v>3.926939606666565</v>
+        <v>4.336418890953064</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.623700857162476</v>
+        <v>5.01624321937561</v>
       </c>
       <c r="C40" t="n">
-        <v>4.621203899383545</v>
+        <v>4.837520599365234</v>
       </c>
       <c r="D40" t="n">
-        <v>4.694023609161377</v>
+        <v>5.330799341201782</v>
       </c>
       <c r="E40" t="n">
-        <v>4.93343448638916</v>
+        <v>4.577719449996948</v>
       </c>
       <c r="F40" t="n">
-        <v>4.482573747634888</v>
+        <v>4.565871715545654</v>
       </c>
       <c r="G40" t="n">
-        <v>4.355896711349487</v>
+        <v>5.223527193069458</v>
       </c>
       <c r="H40" t="n">
-        <v>4.735407114028931</v>
+        <v>4.621390342712402</v>
       </c>
       <c r="I40" t="n">
-        <v>4.600265741348267</v>
+        <v>5.762612819671631</v>
       </c>
       <c r="J40" t="n">
-        <v>4.452650547027588</v>
+        <v>4.791383028030396</v>
       </c>
       <c r="K40" t="n">
-        <v>4.685542106628418</v>
+        <v>4.805925369262695</v>
       </c>
       <c r="L40" t="n">
-        <v>4.618469882011413</v>
+        <v>4.953299307823182</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.449169874191284</v>
+        <v>4.444494009017944</v>
       </c>
       <c r="C41" t="n">
-        <v>4.261120557785034</v>
+        <v>4.540991306304932</v>
       </c>
       <c r="D41" t="n">
-        <v>4.684554576873779</v>
+        <v>4.653618812561035</v>
       </c>
       <c r="E41" t="n">
-        <v>4.704498767852783</v>
+        <v>4.802427768707275</v>
       </c>
       <c r="F41" t="n">
-        <v>4.350392580032349</v>
+        <v>4.990771293640137</v>
       </c>
       <c r="G41" t="n">
-        <v>4.271596908569336</v>
+        <v>4.481202363967896</v>
       </c>
       <c r="H41" t="n">
-        <v>4.059640407562256</v>
+        <v>4.521886348724365</v>
       </c>
       <c r="I41" t="n">
-        <v>4.852163791656494</v>
+        <v>4.621192455291748</v>
       </c>
       <c r="J41" t="n">
-        <v>4.903011798858643</v>
+        <v>4.461843967437744</v>
       </c>
       <c r="K41" t="n">
-        <v>4.038714647293091</v>
+        <v>4.683089017868042</v>
       </c>
       <c r="L41" t="n">
-        <v>4.457486391067505</v>
+        <v>4.620151734352111</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.369886159896851</v>
+        <v>4.771204710006714</v>
       </c>
       <c r="C42" t="n">
-        <v>4.331470727920532</v>
+        <v>4.90168571472168</v>
       </c>
       <c r="D42" t="n">
-        <v>4.309496164321899</v>
+        <v>4.540294647216797</v>
       </c>
       <c r="E42" t="n">
-        <v>4.556860685348511</v>
+        <v>4.622427225112915</v>
       </c>
       <c r="F42" t="n">
-        <v>4.163387060165405</v>
+        <v>4.609762191772461</v>
       </c>
       <c r="G42" t="n">
-        <v>4.3414626121521</v>
+        <v>4.791277170181274</v>
       </c>
       <c r="H42" t="n">
-        <v>4.692535638809204</v>
+        <v>4.575561285018921</v>
       </c>
       <c r="I42" t="n">
-        <v>4.364883184432983</v>
+        <v>4.835351467132568</v>
       </c>
       <c r="J42" t="n">
-        <v>5.54280686378479</v>
+        <v>4.648706436157227</v>
       </c>
       <c r="K42" t="n">
-        <v>4.461628675460815</v>
+        <v>4.48665714263916</v>
       </c>
       <c r="L42" t="n">
-        <v>4.513441777229309</v>
+        <v>4.678292798995972</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>5.635144948959351</v>
+        <v>5.2332603931427</v>
       </c>
       <c r="C43" t="n">
-        <v>4.786269187927246</v>
+        <v>5.083234786987305</v>
       </c>
       <c r="D43" t="n">
-        <v>5.429654836654663</v>
+        <v>4.568609952926636</v>
       </c>
       <c r="E43" t="n">
-        <v>5.072076797485352</v>
+        <v>5.356003761291504</v>
       </c>
       <c r="F43" t="n">
-        <v>4.528918504714966</v>
+        <v>5.060247659683228</v>
       </c>
       <c r="G43" t="n">
-        <v>4.310504674911499</v>
+        <v>5.362287998199463</v>
       </c>
       <c r="H43" t="n">
-        <v>5.130423545837402</v>
+        <v>5.153810262680054</v>
       </c>
       <c r="I43" t="n">
-        <v>4.514526605606079</v>
+        <v>4.994863986968994</v>
       </c>
       <c r="J43" t="n">
-        <v>5.092998027801514</v>
+        <v>4.601992130279541</v>
       </c>
       <c r="K43" t="n">
-        <v>4.634673833847046</v>
+        <v>4.764976024627686</v>
       </c>
       <c r="L43" t="n">
-        <v>4.913519096374512</v>
+        <v>5.017928695678711</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.191815137863159</v>
+        <v>4.460154056549072</v>
       </c>
       <c r="C44" t="n">
-        <v>4.07312798500061</v>
+        <v>4.402375221252441</v>
       </c>
       <c r="D44" t="n">
-        <v>4.383812427520752</v>
+        <v>4.26599907875061</v>
       </c>
       <c r="E44" t="n">
-        <v>4.435698747634888</v>
+        <v>4.877851247787476</v>
       </c>
       <c r="F44" t="n">
-        <v>4.296786308288574</v>
+        <v>4.411730527877808</v>
       </c>
       <c r="G44" t="n">
-        <v>4.388571500778198</v>
+        <v>4.5368971824646</v>
       </c>
       <c r="H44" t="n">
-        <v>4.165647029876709</v>
+        <v>4.302224397659302</v>
       </c>
       <c r="I44" t="n">
-        <v>4.23546028137207</v>
+        <v>4.348904132843018</v>
       </c>
       <c r="J44" t="n">
-        <v>4.279830932617188</v>
+        <v>4.211193084716797</v>
       </c>
       <c r="K44" t="n">
-        <v>4.231990098953247</v>
+        <v>4.472805500030518</v>
       </c>
       <c r="L44" t="n">
-        <v>4.268274044990539</v>
+        <v>4.429013442993164</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.267382144927979</v>
+        <v>4.259728193283081</v>
       </c>
       <c r="C45" t="n">
-        <v>4.101818323135376</v>
+        <v>4.684392690658569</v>
       </c>
       <c r="D45" t="n">
-        <v>4.092164754867554</v>
+        <v>4.57732892036438</v>
       </c>
       <c r="E45" t="n">
-        <v>4.471610069274902</v>
+        <v>4.319737195968628</v>
       </c>
       <c r="F45" t="n">
-        <v>4.053169965744019</v>
+        <v>4.277395248413086</v>
       </c>
       <c r="G45" t="n">
-        <v>3.982826948165894</v>
+        <v>4.296592950820923</v>
       </c>
       <c r="H45" t="n">
-        <v>4.262122869491577</v>
+        <v>4.282899618148804</v>
       </c>
       <c r="I45" t="n">
-        <v>4.188341856002808</v>
+        <v>4.099814414978027</v>
       </c>
       <c r="J45" t="n">
-        <v>4.094062566757202</v>
+        <v>4.421217679977417</v>
       </c>
       <c r="K45" t="n">
-        <v>4.152915716171265</v>
+        <v>4.223205327987671</v>
       </c>
       <c r="L45" t="n">
-        <v>4.166641521453857</v>
+        <v>4.344231224060058</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.408742666244507</v>
+        <v>4.179049730300903</v>
       </c>
       <c r="C46" t="n">
-        <v>4.270637035369873</v>
+        <v>4.125458240509033</v>
       </c>
       <c r="D46" t="n">
-        <v>3.968374967575073</v>
+        <v>4.250530004501343</v>
       </c>
       <c r="E46" t="n">
-        <v>4.171369791030884</v>
+        <v>4.301921606063843</v>
       </c>
       <c r="F46" t="n">
-        <v>4.120977640151978</v>
+        <v>4.577527523040771</v>
       </c>
       <c r="G46" t="n">
-        <v>4.218232393264771</v>
+        <v>4.523199558258057</v>
       </c>
       <c r="H46" t="n">
-        <v>4.568345069885254</v>
+        <v>4.271762371063232</v>
       </c>
       <c r="I46" t="n">
-        <v>4.357385396957397</v>
+        <v>4.648711681365967</v>
       </c>
       <c r="J46" t="n">
-        <v>4.083088636398315</v>
+        <v>4.469532489776611</v>
       </c>
       <c r="K46" t="n">
-        <v>4.216236352920532</v>
+        <v>4.417721509933472</v>
       </c>
       <c r="L46" t="n">
-        <v>4.238338994979858</v>
+        <v>4.376541471481323</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.643134593963623</v>
+        <v>4.457018613815308</v>
       </c>
       <c r="C47" t="n">
-        <v>4.880064964294434</v>
+        <v>4.412519216537476</v>
       </c>
       <c r="D47" t="n">
-        <v>4.865086078643799</v>
+        <v>4.226958036422729</v>
       </c>
       <c r="E47" t="n">
-        <v>4.434685230255127</v>
+        <v>4.902993440628052</v>
       </c>
       <c r="F47" t="n">
-        <v>4.137942790985107</v>
+        <v>4.983858823776245</v>
       </c>
       <c r="G47" t="n">
-        <v>4.799746990203857</v>
+        <v>4.358203649520874</v>
       </c>
       <c r="H47" t="n">
-        <v>5.015205860137939</v>
+        <v>4.479265451431274</v>
       </c>
       <c r="I47" t="n">
-        <v>4.560379505157471</v>
+        <v>4.55019211769104</v>
       </c>
       <c r="J47" t="n">
-        <v>4.392271041870117</v>
+        <v>4.345606088638306</v>
       </c>
       <c r="K47" t="n">
-        <v>4.473167896270752</v>
+        <v>4.734966039657593</v>
       </c>
       <c r="L47" t="n">
-        <v>4.620168495178222</v>
+        <v>4.54515814781189</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.301513910293579</v>
+        <v>4.614073991775513</v>
       </c>
       <c r="C48" t="n">
-        <v>4.202277660369873</v>
+        <v>4.54567289352417</v>
       </c>
       <c r="D48" t="n">
-        <v>4.253130435943604</v>
+        <v>4.424335479736328</v>
       </c>
       <c r="E48" t="n">
-        <v>4.542403221130371</v>
+        <v>5.201413631439209</v>
       </c>
       <c r="F48" t="n">
-        <v>4.460623979568481</v>
+        <v>4.74439263343811</v>
       </c>
       <c r="G48" t="n">
-        <v>4.442644834518433</v>
+        <v>4.789076566696167</v>
       </c>
       <c r="H48" t="n">
-        <v>4.44816517829895</v>
+        <v>4.728604793548584</v>
       </c>
       <c r="I48" t="n">
-        <v>4.491053104400635</v>
+        <v>4.598002433776855</v>
       </c>
       <c r="J48" t="n">
-        <v>4.469604730606079</v>
+        <v>4.515018224716187</v>
       </c>
       <c r="K48" t="n">
-        <v>4.280588150024414</v>
+        <v>4.455776929855347</v>
       </c>
       <c r="L48" t="n">
-        <v>4.389200520515442</v>
+        <v>4.661636757850647</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.784779071807861</v>
+        <v>5.471593141555786</v>
       </c>
       <c r="C49" t="n">
-        <v>4.172848701477051</v>
+        <v>5.423309564590454</v>
       </c>
       <c r="D49" t="n">
-        <v>4.518971681594849</v>
+        <v>4.680203914642334</v>
       </c>
       <c r="E49" t="n">
-        <v>4.52345609664917</v>
+        <v>4.533433675765991</v>
       </c>
       <c r="F49" t="n">
-        <v>4.415730953216553</v>
+        <v>5.133033275604248</v>
       </c>
       <c r="G49" t="n">
-        <v>4.645137548446655</v>
+        <v>5.25195050239563</v>
       </c>
       <c r="H49" t="n">
-        <v>4.648144483566284</v>
+        <v>5.191041469573975</v>
       </c>
       <c r="I49" t="n">
-        <v>4.660648822784424</v>
+        <v>4.390336036682129</v>
       </c>
       <c r="J49" t="n">
-        <v>4.961838960647583</v>
+        <v>4.798155546188354</v>
       </c>
       <c r="K49" t="n">
-        <v>4.261630296707153</v>
+        <v>4.754939317703247</v>
       </c>
       <c r="L49" t="n">
-        <v>4.559318661689758</v>
+        <v>4.962799644470214</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.571918725967407</v>
+        <v>3.991564273834229</v>
       </c>
       <c r="C50" t="n">
-        <v>3.802300214767456</v>
+        <v>3.896108388900757</v>
       </c>
       <c r="D50" t="n">
-        <v>3.693557739257812</v>
+        <v>4.090887308120728</v>
       </c>
       <c r="E50" t="n">
-        <v>3.568905591964722</v>
+        <v>3.982296705245972</v>
       </c>
       <c r="F50" t="n">
-        <v>3.413875102996826</v>
+        <v>3.748623609542847</v>
       </c>
       <c r="G50" t="n">
-        <v>3.605790615081787</v>
+        <v>3.639046669006348</v>
       </c>
       <c r="H50" t="n">
-        <v>3.552441835403442</v>
+        <v>3.836786508560181</v>
       </c>
       <c r="I50" t="n">
-        <v>3.623299121856689</v>
+        <v>4.060215711593628</v>
       </c>
       <c r="J50" t="n">
-        <v>3.430235624313354</v>
+        <v>3.956217050552368</v>
       </c>
       <c r="K50" t="n">
-        <v>3.695063352584839</v>
+        <v>3.876495838165283</v>
       </c>
       <c r="L50" t="n">
-        <v>3.595738792419434</v>
+        <v>3.907824206352234</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.373330116271973</v>
+        <v>5.822758436203003</v>
       </c>
       <c r="C51" t="n">
-        <v>4.20026969909668</v>
+        <v>4.62129282951355</v>
       </c>
       <c r="D51" t="n">
-        <v>4.472103595733643</v>
+        <v>4.630374431610107</v>
       </c>
       <c r="E51" t="n">
-        <v>5.134425401687622</v>
+        <v>4.645360708236694</v>
       </c>
       <c r="F51" t="n">
-        <v>3.9678795337677</v>
+        <v>4.332813262939453</v>
       </c>
       <c r="G51" t="n">
-        <v>4.389298915863037</v>
+        <v>4.503456115722656</v>
       </c>
       <c r="H51" t="n">
-        <v>4.567339181900024</v>
+        <v>4.699899911880493</v>
       </c>
       <c r="I51" t="n">
-        <v>4.377825736999512</v>
+        <v>4.694179773330688</v>
       </c>
       <c r="J51" t="n">
-        <v>4.090552091598511</v>
+        <v>4.865959405899048</v>
       </c>
       <c r="K51" t="n">
-        <v>4.030324220657349</v>
+        <v>4.365647792816162</v>
       </c>
       <c r="L51" t="n">
-        <v>4.360334849357605</v>
+        <v>4.718174266815185</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.433865656852722</v>
+        <v>4.633149542808533</v>
       </c>
       <c r="C52" t="n">
-        <v>4.377249526977539</v>
+        <v>4.615224566459656</v>
       </c>
       <c r="D52" t="n">
-        <v>4.52258454322815</v>
+        <v>4.568158025741577</v>
       </c>
       <c r="E52" t="n">
-        <v>4.463916006088257</v>
+        <v>4.689603447914124</v>
       </c>
       <c r="F52" t="n">
-        <v>4.403969864845276</v>
+        <v>4.701498618125916</v>
       </c>
       <c r="G52" t="n">
-        <v>4.430338687896729</v>
+        <v>4.629650735855103</v>
       </c>
       <c r="H52" t="n">
-        <v>4.44986277103424</v>
+        <v>4.625430307388306</v>
       </c>
       <c r="I52" t="n">
-        <v>4.421611847877503</v>
+        <v>4.62224684715271</v>
       </c>
       <c r="J52" t="n">
-        <v>4.424378628730774</v>
+        <v>4.615682454109192</v>
       </c>
       <c r="K52" t="n">
-        <v>4.458166365623474</v>
+        <v>4.640178732872009</v>
       </c>
       <c r="L52" t="n">
-        <v>4.438594389915466</v>
+        <v>4.634082327842712</v>
       </c>
     </row>
   </sheetData>
